--- a/docs/Data_Dictionary.xlsx
+++ b/docs/Data_Dictionary.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P142"/>
+  <dimension ref="A1:P147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Everyone who uses the system. Login is passwordless via auth_tokens.</t>
+          <t>Everyone who uses the system. Login is passwordless through Supabase Auth (auth.users).</t>
         </is>
       </c>
       <c r="C20" s="2" t="n"/>
@@ -1465,116 +1465,124 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>users</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>auth_user_id</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>UUID</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr"/>
+      <c r="E22" s="4" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>auth.users.id</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr"/>
+      <c r="K22" s="4" t="inlineStr"/>
+      <c r="L22" s="4" t="inlineStr"/>
+      <c r="M22" s="4" t="inlineStr">
+        <is>
+          <t>RESTRICT</t>
+        </is>
+      </c>
+      <c r="N22" s="4" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
+      <c r="O22" s="4" t="inlineStr">
+        <is>
+          <t>Supabase Auth identity (auth.users.id) used to sign in. One-to-one with this row.</t>
+        </is>
+      </c>
+      <c r="P22" s="4" t="inlineStr">
+        <is>
+          <t>Added when auth_tokens was dropped. Created together with the users row by the admin-create-user Edge Function.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>users</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>email_parm_id</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>INTEGER</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr"/>
-      <c r="E22" s="6" t="inlineStr"/>
-      <c r="F22" s="6" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr"/>
+      <c r="E23" s="6" t="inlineStr"/>
+      <c r="F23" s="6" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G22" s="6" t="inlineStr">
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>email_parm.id</t>
         </is>
       </c>
-      <c r="H22" s="6" t="inlineStr">
+      <c r="H23" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I22" s="6" t="inlineStr"/>
-      <c r="J22" s="6" t="inlineStr"/>
-      <c r="K22" s="6" t="inlineStr"/>
-      <c r="L22" s="6" t="inlineStr"/>
-      <c r="M22" s="6" t="inlineStr">
+      <c r="I23" s="6" t="inlineStr"/>
+      <c r="J23" s="6" t="inlineStr"/>
+      <c r="K23" s="6" t="inlineStr"/>
+      <c r="L23" s="6" t="inlineStr"/>
+      <c r="M23" s="6" t="inlineStr">
         <is>
           <t>RESTRICT</t>
         </is>
       </c>
-      <c r="N22" s="6" t="inlineStr">
+      <c r="N23" s="6" t="inlineStr">
         <is>
           <t>NO ACTION</t>
         </is>
       </c>
-      <c r="O22" s="6" t="inlineStr">
+      <c r="O23" s="6" t="inlineStr">
         <is>
           <t>Email format the user's address belongs to.</t>
         </is>
       </c>
-      <c r="P22" s="6" t="inlineStr">
+      <c r="P23" s="6" t="inlineStr">
         <is>
           <t>Assumption: required (every user has an institutional email).</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>users</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>role_id</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr"/>
-      <c r="E23" s="4" t="inlineStr"/>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>role.id</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I23" s="4" t="inlineStr"/>
-      <c r="J23" s="4" t="inlineStr"/>
-      <c r="K23" s="4" t="inlineStr"/>
-      <c r="L23" s="4" t="inlineStr"/>
-      <c r="M23" s="4" t="inlineStr">
-        <is>
-          <t>RESTRICT</t>
-        </is>
-      </c>
-      <c r="N23" s="4" t="inlineStr">
-        <is>
-          <t>NO ACTION</t>
-        </is>
-      </c>
-      <c r="O23" s="4" t="inlineStr">
-        <is>
-          <t>Role assigned to the user.</t>
-        </is>
-      </c>
-      <c r="P23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -1584,22 +1592,26 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>last_name</t>
+          <t>role_id</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr"/>
       <c r="E24" s="4" t="inlineStr"/>
-      <c r="F24" s="4" t="inlineStr"/>
-      <c r="G24" s="4" t="inlineStr"/>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>role.id</t>
+        </is>
+      </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
           <t>No</t>
@@ -1609,11 +1621,19 @@
       <c r="J24" s="4" t="inlineStr"/>
       <c r="K24" s="4" t="inlineStr"/>
       <c r="L24" s="4" t="inlineStr"/>
-      <c r="M24" s="4" t="inlineStr"/>
-      <c r="N24" s="4" t="inlineStr"/>
+      <c r="M24" s="4" t="inlineStr">
+        <is>
+          <t>RESTRICT</t>
+        </is>
+      </c>
+      <c r="N24" s="4" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>User's last name.</t>
+          <t>Role assigned to the user.</t>
         </is>
       </c>
       <c r="P24" s="4" t="inlineStr"/>
@@ -1626,7 +1646,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>first_name</t>
+          <t>last_name</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -1655,7 +1675,7 @@
       <c r="N25" s="4" t="inlineStr"/>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>User's first name.</t>
+          <t>User's last name.</t>
         </is>
       </c>
       <c r="P25" s="4" t="inlineStr"/>
@@ -1668,7 +1688,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>first_name</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -1678,7 +1698,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr"/>
@@ -1689,11 +1709,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I26" s="4" t="inlineStr">
-        <is>
-          <t>Yes (case-insensitive)</t>
-        </is>
-      </c>
+      <c r="I26" s="4" t="inlineStr"/>
       <c r="J26" s="4" t="inlineStr"/>
       <c r="K26" s="4" t="inlineStr"/>
       <c r="L26" s="4" t="inlineStr"/>
@@ -1701,58 +1717,58 @@
       <c r="N26" s="4" t="inlineStr"/>
       <c r="O26" s="4" t="inlineStr">
         <is>
+          <t>User's first name.</t>
+        </is>
+      </c>
+      <c r="P26" s="4" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>users</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr"/>
+      <c r="F27" s="4" t="inlineStr"/>
+      <c r="G27" s="4" t="inlineStr"/>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>Yes (case-insensitive)</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr"/>
+      <c r="K27" s="4" t="inlineStr"/>
+      <c r="L27" s="4" t="inlineStr"/>
+      <c r="M27" s="4" t="inlineStr"/>
+      <c r="N27" s="4" t="inlineStr"/>
+      <c r="O27" s="4" t="inlineStr">
+        <is>
           <t>Login email. Unique ignoring case via index on LOWER(email).</t>
         </is>
       </c>
-      <c r="P26" s="4" t="inlineStr">
+      <c r="P27" s="4" t="inlineStr">
         <is>
           <t>254 is the maximum valid email length.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>users</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>created_at</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>TIMESTAMPTZ</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr"/>
-      <c r="E27" s="5" t="inlineStr"/>
-      <c r="F27" s="5" t="inlineStr"/>
-      <c r="G27" s="5" t="inlineStr"/>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I27" s="5" t="inlineStr"/>
-      <c r="J27" s="5" t="inlineStr"/>
-      <c r="K27" s="5" t="inlineStr">
-        <is>
-          <t>now()</t>
-        </is>
-      </c>
-      <c r="L27" s="5" t="inlineStr"/>
-      <c r="M27" s="5" t="inlineStr"/>
-      <c r="N27" s="5" t="inlineStr"/>
-      <c r="O27" s="5" t="inlineStr">
-        <is>
-          <t>When the row was created.</t>
-        </is>
-      </c>
-      <c r="P27" s="5" t="inlineStr">
-        <is>
-          <t>Audit column.</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1780,7 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -1793,106 +1809,86 @@
       <c r="N28" s="5" t="inlineStr"/>
       <c r="O28" s="5" t="inlineStr">
         <is>
+          <t>When the row was created.</t>
+        </is>
+      </c>
+      <c r="P28" s="5" t="inlineStr">
+        <is>
+          <t>Audit column.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>users</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>TIMESTAMPTZ</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr"/>
+      <c r="E29" s="5" t="inlineStr"/>
+      <c r="F29" s="5" t="inlineStr"/>
+      <c r="G29" s="5" t="inlineStr"/>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr"/>
+      <c r="J29" s="5" t="inlineStr"/>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr"/>
+      <c r="M29" s="5" t="inlineStr"/>
+      <c r="N29" s="5" t="inlineStr"/>
+      <c r="O29" s="5" t="inlineStr">
+        <is>
           <t>When the row was last changed. Set automatically by trigger trg_&lt;table&gt;_updated_at.</t>
         </is>
       </c>
-      <c r="P28" s="5" t="inlineStr">
+      <c r="P29" s="5" t="inlineStr">
         <is>
           <t>Audit column.</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>user_permission</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>Per-user permission overrides that grant or deny on top of the role.</t>
         </is>
       </c>
-      <c r="C29" s="2" t="n"/>
-      <c r="D29" s="2" t="n"/>
-      <c r="E29" s="2" t="n"/>
-      <c r="F29" s="2" t="n"/>
-      <c r="G29" s="2" t="n"/>
-      <c r="H29" s="2" t="n"/>
-      <c r="I29" s="2" t="n"/>
-      <c r="J29" s="2" t="n"/>
-      <c r="K29" s="2" t="n"/>
-      <c r="L29" s="2" t="n"/>
-      <c r="M29" s="2" t="n"/>
-      <c r="N29" s="2" t="n"/>
-      <c r="O29" s="2" t="n"/>
-      <c r="P29" s="2" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>user_permission</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>user_id</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>users.id</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I30" s="3" t="inlineStr"/>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>pk_user_permission</t>
-        </is>
-      </c>
-      <c r="K30" s="3" t="inlineStr"/>
-      <c r="L30" s="3" t="inlineStr"/>
-      <c r="M30" s="3" t="inlineStr">
-        <is>
-          <t>CASCADE</t>
-        </is>
-      </c>
-      <c r="N30" s="3" t="inlineStr">
-        <is>
-          <t>CASCADE</t>
-        </is>
-      </c>
-      <c r="O30" s="3" t="inlineStr">
-        <is>
-          <t>User the override applies to.</t>
-        </is>
-      </c>
-      <c r="P30" s="3" t="inlineStr"/>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n"/>
+      <c r="E30" s="2" t="n"/>
+      <c r="F30" s="2" t="n"/>
+      <c r="G30" s="2" t="n"/>
+      <c r="H30" s="2" t="n"/>
+      <c r="I30" s="2" t="n"/>
+      <c r="J30" s="2" t="n"/>
+      <c r="K30" s="2" t="n"/>
+      <c r="L30" s="2" t="n"/>
+      <c r="M30" s="2" t="n"/>
+      <c r="N30" s="2" t="n"/>
+      <c r="O30" s="2" t="n"/>
+      <c r="P30" s="2" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -1902,15 +1898,19 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>permission_id</t>
+          <t>user_id</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr"/>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>permissions.id</t>
+          <t>users.id</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
@@ -1946,103 +1946,119 @@
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
+          <t>CASCADE</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t>User the override applies to.</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>user_permission</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>permission_id</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr"/>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>permissions.id</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr"/>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>pk_user_permission</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr"/>
+      <c r="L32" s="3" t="inlineStr"/>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>CASCADE</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
           <t>NO ACTION</t>
         </is>
       </c>
-      <c r="O31" s="3" t="inlineStr">
+      <c r="O32" s="3" t="inlineStr">
         <is>
           <t>Permission being granted or denied.</t>
         </is>
       </c>
-      <c r="P31" s="3" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="P32" s="3" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>user_permission</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>modifier_type</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>ENUM</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>modifier_type</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr"/>
-      <c r="F32" s="4" t="inlineStr"/>
-      <c r="G32" s="4" t="inlineStr"/>
-      <c r="H32" s="4" t="inlineStr">
+      <c r="E33" s="4" t="inlineStr"/>
+      <c r="F33" s="4" t="inlineStr"/>
+      <c r="G33" s="4" t="inlineStr"/>
+      <c r="H33" s="4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I32" s="4" t="inlineStr"/>
-      <c r="J32" s="4" t="inlineStr"/>
-      <c r="K32" s="4" t="inlineStr"/>
-      <c r="L32" s="4" t="inlineStr"/>
-      <c r="M32" s="4" t="inlineStr"/>
-      <c r="N32" s="4" t="inlineStr"/>
-      <c r="O32" s="4" t="inlineStr">
+      <c r="I33" s="4" t="inlineStr"/>
+      <c r="J33" s="4" t="inlineStr"/>
+      <c r="K33" s="4" t="inlineStr"/>
+      <c r="L33" s="4" t="inlineStr"/>
+      <c r="M33" s="4" t="inlineStr"/>
+      <c r="N33" s="4" t="inlineStr"/>
+      <c r="O33" s="4" t="inlineStr">
         <is>
           <t>grant = add permission, deny = remove it even if the role has it.</t>
         </is>
       </c>
-      <c r="P32" s="4" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>user_permission</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>created_at</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>TIMESTAMPTZ</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr"/>
-      <c r="E33" s="5" t="inlineStr"/>
-      <c r="F33" s="5" t="inlineStr"/>
-      <c r="G33" s="5" t="inlineStr"/>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I33" s="5" t="inlineStr"/>
-      <c r="J33" s="5" t="inlineStr"/>
-      <c r="K33" s="5" t="inlineStr">
-        <is>
-          <t>now()</t>
-        </is>
-      </c>
-      <c r="L33" s="5" t="inlineStr"/>
-      <c r="M33" s="5" t="inlineStr"/>
-      <c r="N33" s="5" t="inlineStr"/>
-      <c r="O33" s="5" t="inlineStr">
-        <is>
-          <t>When the row was created.</t>
-        </is>
-      </c>
-      <c r="P33" s="5" t="inlineStr">
-        <is>
-          <t>Audit column.</t>
-        </is>
-      </c>
+      <c r="P33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -2052,7 +2068,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -2081,7 +2097,7 @@
       <c r="N34" s="5" t="inlineStr"/>
       <c r="O34" s="5" t="inlineStr">
         <is>
-          <t>When the row was last changed. Set automatically by trigger trg_&lt;table&gt;_updated_at.</t>
+          <t>When the row was created.</t>
         </is>
       </c>
       <c r="P34" s="5" t="inlineStr">
@@ -2098,52 +2114,36 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>created_by</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>TIMESTAMPTZ</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr"/>
       <c r="E35" s="5" t="inlineStr"/>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G35" s="5" t="inlineStr">
-        <is>
-          <t>users.id</t>
-        </is>
-      </c>
+      <c r="F35" s="5" t="inlineStr"/>
+      <c r="G35" s="5" t="inlineStr"/>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr"/>
       <c r="J35" s="5" t="inlineStr"/>
-      <c r="K35" s="5" t="inlineStr"/>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
       <c r="L35" s="5" t="inlineStr"/>
-      <c r="M35" s="5" t="inlineStr">
-        <is>
-          <t>SET NULL</t>
-        </is>
-      </c>
-      <c r="N35" s="5" t="inlineStr">
-        <is>
-          <t>CASCADE</t>
-        </is>
-      </c>
+      <c r="M35" s="5" t="inlineStr"/>
+      <c r="N35" s="5" t="inlineStr"/>
       <c r="O35" s="5" t="inlineStr">
         <is>
-          <t>User who created the row. NULL for system-generated rows (e.g. automatic check-ins).</t>
+          <t>When the row was last changed. Set automatically by trigger trg_&lt;table&gt;_updated_at.</t>
         </is>
       </c>
       <c r="P35" s="5" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>updated_by</t>
+          <t>created_by</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
@@ -2205,102 +2205,102 @@
       </c>
       <c r="O36" s="5" t="inlineStr">
         <is>
+          <t>User who created the row. NULL for system-generated rows (e.g. automatic check-ins).</t>
+        </is>
+      </c>
+      <c r="P36" s="5" t="inlineStr">
+        <is>
+          <t>Audit column.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>user_permission</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>updated_by</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr"/>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>users.id</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr"/>
+      <c r="J37" s="5" t="inlineStr"/>
+      <c r="K37" s="5" t="inlineStr"/>
+      <c r="L37" s="5" t="inlineStr"/>
+      <c r="M37" s="5" t="inlineStr">
+        <is>
+          <t>SET NULL</t>
+        </is>
+      </c>
+      <c r="N37" s="5" t="inlineStr">
+        <is>
+          <t>CASCADE</t>
+        </is>
+      </c>
+      <c r="O37" s="5" t="inlineStr">
+        <is>
           <t>User who last changed the row. Set by the application.</t>
         </is>
       </c>
-      <c r="P36" s="5" t="inlineStr">
+      <c r="P37" s="5" t="inlineStr">
         <is>
           <t>Audit column.</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>role_permission</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>Permissions every user with a role receives.</t>
         </is>
       </c>
-      <c r="C37" s="2" t="n"/>
-      <c r="D37" s="2" t="n"/>
-      <c r="E37" s="2" t="n"/>
-      <c r="F37" s="2" t="n"/>
-      <c r="G37" s="2" t="n"/>
-      <c r="H37" s="2" t="n"/>
-      <c r="I37" s="2" t="n"/>
-      <c r="J37" s="2" t="n"/>
-      <c r="K37" s="2" t="n"/>
-      <c r="L37" s="2" t="n"/>
-      <c r="M37" s="2" t="n"/>
-      <c r="N37" s="2" t="n"/>
-      <c r="O37" s="2" t="n"/>
-      <c r="P37" s="2" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>role_permission</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>role_id</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr"/>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F38" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t>role.id</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I38" s="3" t="inlineStr"/>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>pk_role_permission</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="inlineStr"/>
-      <c r="L38" s="3" t="inlineStr"/>
-      <c r="M38" s="3" t="inlineStr">
-        <is>
-          <t>CASCADE</t>
-        </is>
-      </c>
-      <c r="N38" s="3" t="inlineStr">
-        <is>
-          <t>NO ACTION</t>
-        </is>
-      </c>
-      <c r="O38" s="3" t="inlineStr">
-        <is>
-          <t>Role receiving the permission.</t>
-        </is>
-      </c>
-      <c r="P38" s="3" t="inlineStr"/>
+      <c r="C38" s="2" t="n"/>
+      <c r="D38" s="2" t="n"/>
+      <c r="E38" s="2" t="n"/>
+      <c r="F38" s="2" t="n"/>
+      <c r="G38" s="2" t="n"/>
+      <c r="H38" s="2" t="n"/>
+      <c r="I38" s="2" t="n"/>
+      <c r="J38" s="2" t="n"/>
+      <c r="K38" s="2" t="n"/>
+      <c r="L38" s="2" t="n"/>
+      <c r="M38" s="2" t="n"/>
+      <c r="N38" s="2" t="n"/>
+      <c r="O38" s="2" t="n"/>
+      <c r="P38" s="2" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>permission_id</t>
+          <t>role_id</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>permissions.id</t>
+          <t>role.id</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
@@ -2359,56 +2359,72 @@
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
+          <t>Role receiving the permission.</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>role_permission</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>permission_id</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr"/>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>permissions.id</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr"/>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>pk_role_permission</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr"/>
+      <c r="L40" s="3" t="inlineStr"/>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>CASCADE</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
           <t>Permission given to the role.</t>
         </is>
       </c>
-      <c r="P39" s="3" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>role_permission</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t>created_at</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>TIMESTAMPTZ</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="inlineStr"/>
-      <c r="E40" s="5" t="inlineStr"/>
-      <c r="F40" s="5" t="inlineStr"/>
-      <c r="G40" s="5" t="inlineStr"/>
-      <c r="H40" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I40" s="5" t="inlineStr"/>
-      <c r="J40" s="5" t="inlineStr"/>
-      <c r="K40" s="5" t="inlineStr">
-        <is>
-          <t>now()</t>
-        </is>
-      </c>
-      <c r="L40" s="5" t="inlineStr"/>
-      <c r="M40" s="5" t="inlineStr"/>
-      <c r="N40" s="5" t="inlineStr"/>
-      <c r="O40" s="5" t="inlineStr">
-        <is>
-          <t>When the row was created.</t>
-        </is>
-      </c>
-      <c r="P40" s="5" t="inlineStr">
-        <is>
-          <t>Audit column.</t>
-        </is>
-      </c>
+      <c r="P40" s="3" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -2418,7 +2434,7 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -2447,7 +2463,7 @@
       <c r="N41" s="5" t="inlineStr"/>
       <c r="O41" s="5" t="inlineStr">
         <is>
-          <t>When the row was last changed. Set automatically by trigger trg_&lt;table&gt;_updated_at.</t>
+          <t>When the row was created.</t>
         </is>
       </c>
       <c r="P41" s="5" t="inlineStr">
@@ -2464,52 +2480,36 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>created_by</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>TIMESTAMPTZ</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr"/>
       <c r="E42" s="5" t="inlineStr"/>
-      <c r="F42" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G42" s="5" t="inlineStr">
-        <is>
-          <t>users.id</t>
-        </is>
-      </c>
+      <c r="F42" s="5" t="inlineStr"/>
+      <c r="G42" s="5" t="inlineStr"/>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I42" s="5" t="inlineStr"/>
       <c r="J42" s="5" t="inlineStr"/>
-      <c r="K42" s="5" t="inlineStr"/>
+      <c r="K42" s="5" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
       <c r="L42" s="5" t="inlineStr"/>
-      <c r="M42" s="5" t="inlineStr">
-        <is>
-          <t>SET NULL</t>
-        </is>
-      </c>
-      <c r="N42" s="5" t="inlineStr">
-        <is>
-          <t>CASCADE</t>
-        </is>
-      </c>
+      <c r="M42" s="5" t="inlineStr"/>
+      <c r="N42" s="5" t="inlineStr"/>
       <c r="O42" s="5" t="inlineStr">
         <is>
-          <t>User who created the row. NULL for system-generated rows (e.g. automatic check-ins).</t>
+          <t>When the row was last changed. Set automatically by trigger trg_&lt;table&gt;_updated_at.</t>
         </is>
       </c>
       <c r="P42" s="5" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>updated_by</t>
+          <t>created_by</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -2571,162 +2571,162 @@
       </c>
       <c r="O43" s="5" t="inlineStr">
         <is>
+          <t>User who created the row. NULL for system-generated rows (e.g. automatic check-ins).</t>
+        </is>
+      </c>
+      <c r="P43" s="5" t="inlineStr">
+        <is>
+          <t>Audit column.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>role_permission</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>updated_by</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr"/>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>users.id</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr"/>
+      <c r="J44" s="5" t="inlineStr"/>
+      <c r="K44" s="5" t="inlineStr"/>
+      <c r="L44" s="5" t="inlineStr"/>
+      <c r="M44" s="5" t="inlineStr">
+        <is>
+          <t>SET NULL</t>
+        </is>
+      </c>
+      <c r="N44" s="5" t="inlineStr">
+        <is>
+          <t>CASCADE</t>
+        </is>
+      </c>
+      <c r="O44" s="5" t="inlineStr">
+        <is>
           <t>User who last changed the row. Set by the application.</t>
         </is>
       </c>
-      <c r="P43" s="5" t="inlineStr">
+      <c r="P44" s="5" t="inlineStr">
         <is>
           <t>Audit column.</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>auth_tokens</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>One-time login tokens for passwordless sign-in.</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="n"/>
-      <c r="D44" s="2" t="n"/>
-      <c r="E44" s="2" t="n"/>
-      <c r="F44" s="2" t="n"/>
-      <c r="G44" s="2" t="n"/>
-      <c r="H44" s="2" t="n"/>
-      <c r="I44" s="2" t="n"/>
-      <c r="J44" s="2" t="n"/>
-      <c r="K44" s="2" t="n"/>
-      <c r="L44" s="2" t="n"/>
-      <c r="M44" s="2" t="n"/>
-      <c r="N44" s="2" t="n"/>
-      <c r="O44" s="2" t="n"/>
-      <c r="P44" s="2" t="n"/>
-    </row>
     <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>auth_tokens</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>frequency</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>How often a scheduled class repeats.</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="n"/>
+      <c r="D45" s="2" t="n"/>
+      <c r="E45" s="2" t="n"/>
+      <c r="F45" s="2" t="n"/>
+      <c r="G45" s="2" t="n"/>
+      <c r="H45" s="2" t="n"/>
+      <c r="I45" s="2" t="n"/>
+      <c r="J45" s="2" t="n"/>
+      <c r="K45" s="2" t="n"/>
+      <c r="L45" s="2" t="n"/>
+      <c r="M45" s="2" t="n"/>
+      <c r="N45" s="2" t="n"/>
+      <c r="O45" s="2" t="n"/>
+      <c r="P45" s="2" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>frequency</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="inlineStr"/>
-      <c r="E45" s="3" t="inlineStr">
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr"/>
+      <c r="E46" s="3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F45" s="3" t="inlineStr"/>
-      <c r="G45" s="3" t="inlineStr"/>
-      <c r="H45" s="3" t="inlineStr">
+      <c r="F46" s="3" t="inlineStr"/>
+      <c r="G46" s="3" t="inlineStr"/>
+      <c r="H46" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I45" s="3" t="inlineStr">
+      <c r="I46" s="3" t="inlineStr">
         <is>
           <t>Yes (PK)</t>
         </is>
       </c>
-      <c r="J45" s="3" t="inlineStr"/>
-      <c r="K45" s="3" t="inlineStr">
+      <c r="J46" s="3" t="inlineStr"/>
+      <c r="K46" s="3" t="inlineStr">
         <is>
           <t>IDENTITY</t>
         </is>
       </c>
-      <c r="L45" s="3" t="inlineStr"/>
-      <c r="M45" s="3" t="inlineStr"/>
-      <c r="N45" s="3" t="inlineStr"/>
-      <c r="O45" s="3" t="inlineStr">
-        <is>
-          <t>Unique identifier of the token.</t>
-        </is>
-      </c>
-      <c r="P45" s="3" t="inlineStr">
-        <is>
-          <t>BIGINT because tokens accumulate quickly.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>auth_tokens</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>user_id</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="D46" s="4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E46" s="4" t="inlineStr"/>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G46" s="4" t="inlineStr">
-        <is>
-          <t>users.id</t>
-        </is>
-      </c>
-      <c r="H46" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I46" s="4" t="inlineStr"/>
-      <c r="J46" s="4" t="inlineStr"/>
-      <c r="K46" s="4" t="inlineStr"/>
-      <c r="L46" s="4" t="inlineStr"/>
-      <c r="M46" s="4" t="inlineStr">
-        <is>
-          <t>CASCADE</t>
-        </is>
-      </c>
-      <c r="N46" s="4" t="inlineStr">
-        <is>
-          <t>CASCADE</t>
-        </is>
-      </c>
-      <c r="O46" s="4" t="inlineStr">
-        <is>
-          <t>User the token was issued to.</t>
-        </is>
-      </c>
-      <c r="P46" s="4" t="inlineStr"/>
+      <c r="L46" s="3" t="inlineStr"/>
+      <c r="M46" s="3" t="inlineStr"/>
+      <c r="N46" s="3" t="inlineStr"/>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t>Unique identifier of the frequency.</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>auth_tokens</t>
+          <t>frequency</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>token_hash</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>50</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr"/>
@@ -2759,7 +2759,7 @@
       <c r="N47" s="4" t="inlineStr"/>
       <c r="O47" s="4" t="inlineStr">
         <is>
-          <t>Hash of the token sent to the user. The raw token is never stored.</t>
+          <t>Label, e.g. weekly, fortnightly.</t>
         </is>
       </c>
       <c r="P47" s="4" t="inlineStr"/>
@@ -2767,17 +2767,17 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>auth_tokens</t>
+          <t>frequency</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>interval_days</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>TIMESTAMPTZ</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr"/>
@@ -2791,131 +2791,131 @@
       </c>
       <c r="I48" s="4" t="inlineStr"/>
       <c r="J48" s="4" t="inlineStr"/>
-      <c r="K48" s="4" t="inlineStr">
-        <is>
-          <t>now()</t>
-        </is>
-      </c>
-      <c r="L48" s="4" t="inlineStr"/>
+      <c r="K48" s="4" t="inlineStr"/>
+      <c r="L48" s="4" t="inlineStr">
+        <is>
+          <t>interval_days &gt; 0</t>
+        </is>
+      </c>
       <c r="M48" s="4" t="inlineStr"/>
       <c r="N48" s="4" t="inlineStr"/>
       <c r="O48" s="4" t="inlineStr">
         <is>
-          <t>When the token was issued.</t>
+          <t>Days between occurrences, e.g. 7 or 14.</t>
         </is>
       </c>
       <c r="P48" s="4" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>auth_tokens</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>expires_at</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>TIMESTAMPTZ</t>
-        </is>
-      </c>
-      <c r="D49" s="4" t="inlineStr"/>
-      <c r="E49" s="4" t="inlineStr"/>
-      <c r="F49" s="4" t="inlineStr"/>
-      <c r="G49" s="4" t="inlineStr"/>
-      <c r="H49" s="4" t="inlineStr">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>academic_period</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Terms or semesters that schedules belong to.</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="n"/>
+      <c r="D49" s="2" t="n"/>
+      <c r="E49" s="2" t="n"/>
+      <c r="F49" s="2" t="n"/>
+      <c r="G49" s="2" t="n"/>
+      <c r="H49" s="2" t="n"/>
+      <c r="I49" s="2" t="n"/>
+      <c r="J49" s="2" t="n"/>
+      <c r="K49" s="2" t="n"/>
+      <c r="L49" s="2" t="n"/>
+      <c r="M49" s="2" t="n"/>
+      <c r="N49" s="2" t="n"/>
+      <c r="O49" s="2" t="n"/>
+      <c r="P49" s="2" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>academic_period</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr"/>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr"/>
+      <c r="G50" s="3" t="inlineStr"/>
+      <c r="H50" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I49" s="4" t="inlineStr"/>
-      <c r="J49" s="4" t="inlineStr"/>
-      <c r="K49" s="4" t="inlineStr"/>
-      <c r="L49" s="4" t="inlineStr"/>
-      <c r="M49" s="4" t="inlineStr"/>
-      <c r="N49" s="4" t="inlineStr"/>
-      <c r="O49" s="4" t="inlineStr">
-        <is>
-          <t>When the token stops being valid.</t>
-        </is>
-      </c>
-      <c r="P49" s="4" t="inlineStr">
-        <is>
-          <t>Replaces ERD 'float: validTime'. Must be later than created_at (see Composite Constraints).</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>auth_tokens</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>used</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>BOOLEAN</t>
-        </is>
-      </c>
-      <c r="D50" s="4" t="inlineStr"/>
-      <c r="E50" s="4" t="inlineStr"/>
-      <c r="F50" s="4" t="inlineStr"/>
-      <c r="G50" s="4" t="inlineStr"/>
-      <c r="H50" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I50" s="4" t="inlineStr"/>
-      <c r="J50" s="4" t="inlineStr"/>
-      <c r="K50" s="4" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="L50" s="4" t="inlineStr"/>
-      <c r="M50" s="4" t="inlineStr"/>
-      <c r="N50" s="4" t="inlineStr"/>
-      <c r="O50" s="4" t="inlineStr">
-        <is>
-          <t>True once the token has been used to log in.</t>
-        </is>
-      </c>
-      <c r="P50" s="4" t="inlineStr"/>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>Yes (PK)</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr"/>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>IDENTITY</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr"/>
+      <c r="M50" s="3" t="inlineStr"/>
+      <c r="N50" s="3" t="inlineStr"/>
+      <c r="O50" s="3" t="inlineStr">
+        <is>
+          <t>Unique identifier of the period.</t>
+        </is>
+      </c>
+      <c r="P50" s="3" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>auth_tokens</t>
+          <t>academic_period</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>ip_address</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>INET</t>
-        </is>
-      </c>
-      <c r="D51" s="4" t="inlineStr"/>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="E51" s="4" t="inlineStr"/>
       <c r="F51" s="4" t="inlineStr"/>
       <c r="G51" s="4" t="inlineStr"/>
       <c r="H51" s="4" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="I51" s="4" t="inlineStr"/>
       <c r="J51" s="4" t="inlineStr"/>
       <c r="K51" s="4" t="inlineStr"/>
       <c r="L51" s="4" t="inlineStr"/>
@@ -2923,7 +2923,7 @@
       <c r="N51" s="4" t="inlineStr"/>
       <c r="O51" s="4" t="inlineStr">
         <is>
-          <t>IP address that requested the token. INET stores IPv4 and IPv6.</t>
+          <t>Period name, e.g. 2026 Term 4.</t>
         </is>
       </c>
       <c r="P51" s="4" t="inlineStr"/>
@@ -2931,30 +2931,26 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>auth_tokens</t>
+          <t>academic_period</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>start_date</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="D52" s="4" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr"/>
       <c r="E52" s="4" t="inlineStr"/>
       <c r="F52" s="4" t="inlineStr"/>
       <c r="G52" s="4" t="inlineStr"/>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr"/>
@@ -2965,184 +2961,196 @@
       <c r="N52" s="4" t="inlineStr"/>
       <c r="O52" s="4" t="inlineStr">
         <is>
-          <t>Device or user agent that requested the token.</t>
+          <t>First day of the period.</t>
         </is>
       </c>
       <c r="P52" s="4" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>frequency</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>How often a scheduled class repeats.</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="n"/>
-      <c r="D53" s="2" t="n"/>
-      <c r="E53" s="2" t="n"/>
-      <c r="F53" s="2" t="n"/>
-      <c r="G53" s="2" t="n"/>
-      <c r="H53" s="2" t="n"/>
-      <c r="I53" s="2" t="n"/>
-      <c r="J53" s="2" t="n"/>
-      <c r="K53" s="2" t="n"/>
-      <c r="L53" s="2" t="n"/>
-      <c r="M53" s="2" t="n"/>
-      <c r="N53" s="2" t="n"/>
-      <c r="O53" s="2" t="n"/>
-      <c r="P53" s="2" t="n"/>
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>academic_period</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>finish_date</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr"/>
+      <c r="E53" s="4" t="inlineStr"/>
+      <c r="F53" s="4" t="inlineStr"/>
+      <c r="G53" s="4" t="inlineStr"/>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I53" s="4" t="inlineStr"/>
+      <c r="J53" s="4" t="inlineStr"/>
+      <c r="K53" s="4" t="inlineStr"/>
+      <c r="L53" s="4" t="inlineStr"/>
+      <c r="M53" s="4" t="inlineStr"/>
+      <c r="N53" s="4" t="inlineStr"/>
+      <c r="O53" s="4" t="inlineStr">
+        <is>
+          <t>Last day of the period. Must be after start_date.</t>
+        </is>
+      </c>
+      <c r="P53" s="4" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>frequency</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="C54" s="3" t="inlineStr">
-        <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="D54" s="3" t="inlineStr"/>
-      <c r="E54" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F54" s="3" t="inlineStr"/>
-      <c r="G54" s="3" t="inlineStr"/>
-      <c r="H54" s="3" t="inlineStr">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>academic_period</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>ENUM</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>academic_period_status</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr"/>
+      <c r="F54" s="4" t="inlineStr"/>
+      <c r="G54" s="4" t="inlineStr"/>
+      <c r="H54" s="4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I54" s="3" t="inlineStr">
-        <is>
-          <t>Yes (PK)</t>
-        </is>
-      </c>
-      <c r="J54" s="3" t="inlineStr"/>
-      <c r="K54" s="3" t="inlineStr">
-        <is>
-          <t>IDENTITY</t>
-        </is>
-      </c>
-      <c r="L54" s="3" t="inlineStr"/>
-      <c r="M54" s="3" t="inlineStr"/>
-      <c r="N54" s="3" t="inlineStr"/>
-      <c r="O54" s="3" t="inlineStr">
-        <is>
-          <t>Unique identifier of the frequency.</t>
-        </is>
-      </c>
-      <c r="P54" s="3" t="inlineStr"/>
+      <c r="I54" s="4" t="inlineStr"/>
+      <c r="J54" s="4" t="inlineStr"/>
+      <c r="K54" s="4" t="inlineStr">
+        <is>
+          <t>'planning'</t>
+        </is>
+      </c>
+      <c r="L54" s="4" t="inlineStr"/>
+      <c r="M54" s="4" t="inlineStr"/>
+      <c r="N54" s="4" t="inlineStr"/>
+      <c r="O54" s="4" t="inlineStr">
+        <is>
+          <t>planning, active or finished.</t>
+        </is>
+      </c>
+      <c r="P54" s="4" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>frequency</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="D55" s="4" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="E55" s="4" t="inlineStr"/>
-      <c r="F55" s="4" t="inlineStr"/>
-      <c r="G55" s="4" t="inlineStr"/>
-      <c r="H55" s="4" t="inlineStr">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>academic_period</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>TIMESTAMPTZ</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr"/>
+      <c r="E55" s="5" t="inlineStr"/>
+      <c r="F55" s="5" t="inlineStr"/>
+      <c r="G55" s="5" t="inlineStr"/>
+      <c r="H55" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I55" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J55" s="4" t="inlineStr"/>
-      <c r="K55" s="4" t="inlineStr"/>
-      <c r="L55" s="4" t="inlineStr"/>
-      <c r="M55" s="4" t="inlineStr"/>
-      <c r="N55" s="4" t="inlineStr"/>
-      <c r="O55" s="4" t="inlineStr">
-        <is>
-          <t>Label, e.g. weekly, fortnightly.</t>
-        </is>
-      </c>
-      <c r="P55" s="4" t="inlineStr"/>
+      <c r="I55" s="5" t="inlineStr"/>
+      <c r="J55" s="5" t="inlineStr"/>
+      <c r="K55" s="5" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
+      <c r="L55" s="5" t="inlineStr"/>
+      <c r="M55" s="5" t="inlineStr"/>
+      <c r="N55" s="5" t="inlineStr"/>
+      <c r="O55" s="5" t="inlineStr">
+        <is>
+          <t>When the row was created.</t>
+        </is>
+      </c>
+      <c r="P55" s="5" t="inlineStr">
+        <is>
+          <t>Audit column.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>frequency</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t>interval_days</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="inlineStr">
-        <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="D56" s="4" t="inlineStr"/>
-      <c r="E56" s="4" t="inlineStr"/>
-      <c r="F56" s="4" t="inlineStr"/>
-      <c r="G56" s="4" t="inlineStr"/>
-      <c r="H56" s="4" t="inlineStr">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>academic_period</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>TIMESTAMPTZ</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr"/>
+      <c r="E56" s="5" t="inlineStr"/>
+      <c r="F56" s="5" t="inlineStr"/>
+      <c r="G56" s="5" t="inlineStr"/>
+      <c r="H56" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I56" s="4" t="inlineStr"/>
-      <c r="J56" s="4" t="inlineStr"/>
-      <c r="K56" s="4" t="inlineStr"/>
-      <c r="L56" s="4" t="inlineStr">
-        <is>
-          <t>interval_days &gt; 0</t>
-        </is>
-      </c>
-      <c r="M56" s="4" t="inlineStr"/>
-      <c r="N56" s="4" t="inlineStr"/>
-      <c r="O56" s="4" t="inlineStr">
-        <is>
-          <t>Days between occurrences, e.g. 7 or 14.</t>
-        </is>
-      </c>
-      <c r="P56" s="4" t="inlineStr"/>
+      <c r="I56" s="5" t="inlineStr"/>
+      <c r="J56" s="5" t="inlineStr"/>
+      <c r="K56" s="5" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
+      <c r="L56" s="5" t="inlineStr"/>
+      <c r="M56" s="5" t="inlineStr"/>
+      <c r="N56" s="5" t="inlineStr"/>
+      <c r="O56" s="5" t="inlineStr">
+        <is>
+          <t>When the row was last changed. Set automatically by trigger trg_&lt;table&gt;_updated_at.</t>
+        </is>
+      </c>
+      <c r="P56" s="5" t="inlineStr">
+        <is>
+          <t>Audit column.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>academic_period</t>
+          <t>class</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Terms or semesters that schedules belong to.</t>
+          <t>Subjects or units offered.</t>
         </is>
       </c>
       <c r="C57" s="2" t="n"/>
@@ -3163,7 +3171,7 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>academic_period</t>
+          <t>class</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -3205,7 +3213,7 @@
       <c r="N58" s="3" t="inlineStr"/>
       <c r="O58" s="3" t="inlineStr">
         <is>
-          <t>Unique identifier of the period.</t>
+          <t>Unique identifier of the class.</t>
         </is>
       </c>
       <c r="P58" s="3" t="inlineStr"/>
@@ -3213,7 +3221,7 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>academic_period</t>
+          <t>class</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
@@ -3228,7 +3236,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>150</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr"/>
@@ -3251,7 +3259,7 @@
       <c r="N59" s="4" t="inlineStr"/>
       <c r="O59" s="4" t="inlineStr">
         <is>
-          <t>Period name, e.g. 2026 Term 4.</t>
+          <t>Class name.</t>
         </is>
       </c>
       <c r="P59" s="4" t="inlineStr"/>
@@ -3259,17 +3267,17 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>academic_period</t>
+          <t>class</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>start_date</t>
+          <t>description</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr"/>
@@ -3278,7 +3286,7 @@
       <c r="G60" s="4" t="inlineStr"/>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I60" s="4" t="inlineStr"/>
@@ -3289,579 +3297,611 @@
       <c r="N60" s="4" t="inlineStr"/>
       <c r="O60" s="4" t="inlineStr">
         <is>
-          <t>First day of the period.</t>
+          <t>Class description.</t>
         </is>
       </c>
       <c r="P60" s="4" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="inlineStr">
-        <is>
-          <t>academic_period</t>
-        </is>
-      </c>
-      <c r="B61" s="4" t="inlineStr">
-        <is>
-          <t>finish_date</t>
-        </is>
-      </c>
-      <c r="C61" s="4" t="inlineStr">
-        <is>
-          <t>DATE</t>
-        </is>
-      </c>
-      <c r="D61" s="4" t="inlineStr"/>
-      <c r="E61" s="4" t="inlineStr"/>
-      <c r="F61" s="4" t="inlineStr"/>
-      <c r="G61" s="4" t="inlineStr"/>
-      <c r="H61" s="4" t="inlineStr">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>class</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>TIMESTAMPTZ</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr"/>
+      <c r="E61" s="5" t="inlineStr"/>
+      <c r="F61" s="5" t="inlineStr"/>
+      <c r="G61" s="5" t="inlineStr"/>
+      <c r="H61" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I61" s="4" t="inlineStr"/>
-      <c r="J61" s="4" t="inlineStr"/>
-      <c r="K61" s="4" t="inlineStr"/>
-      <c r="L61" s="4" t="inlineStr"/>
-      <c r="M61" s="4" t="inlineStr"/>
-      <c r="N61" s="4" t="inlineStr"/>
-      <c r="O61" s="4" t="inlineStr">
-        <is>
-          <t>Last day of the period. Must be after start_date.</t>
-        </is>
-      </c>
-      <c r="P61" s="4" t="inlineStr"/>
+      <c r="I61" s="5" t="inlineStr"/>
+      <c r="J61" s="5" t="inlineStr"/>
+      <c r="K61" s="5" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
+      <c r="L61" s="5" t="inlineStr"/>
+      <c r="M61" s="5" t="inlineStr"/>
+      <c r="N61" s="5" t="inlineStr"/>
+      <c r="O61" s="5" t="inlineStr">
+        <is>
+          <t>When the row was created.</t>
+        </is>
+      </c>
+      <c r="P61" s="5" t="inlineStr">
+        <is>
+          <t>Audit column.</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" s="4" t="inlineStr">
-        <is>
-          <t>academic_period</t>
-        </is>
-      </c>
-      <c r="B62" s="4" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="C62" s="4" t="inlineStr">
-        <is>
-          <t>ENUM</t>
-        </is>
-      </c>
-      <c r="D62" s="4" t="inlineStr">
-        <is>
-          <t>academic_period_status</t>
-        </is>
-      </c>
-      <c r="E62" s="4" t="inlineStr"/>
-      <c r="F62" s="4" t="inlineStr"/>
-      <c r="G62" s="4" t="inlineStr"/>
-      <c r="H62" s="4" t="inlineStr">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>class</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>TIMESTAMPTZ</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr"/>
+      <c r="E62" s="5" t="inlineStr"/>
+      <c r="F62" s="5" t="inlineStr"/>
+      <c r="G62" s="5" t="inlineStr"/>
+      <c r="H62" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I62" s="4" t="inlineStr"/>
-      <c r="J62" s="4" t="inlineStr"/>
-      <c r="K62" s="4" t="inlineStr">
-        <is>
-          <t>'planning'</t>
-        </is>
-      </c>
-      <c r="L62" s="4" t="inlineStr"/>
-      <c r="M62" s="4" t="inlineStr"/>
-      <c r="N62" s="4" t="inlineStr"/>
-      <c r="O62" s="4" t="inlineStr">
-        <is>
-          <t>planning, active or finished.</t>
-        </is>
-      </c>
-      <c r="P62" s="4" t="inlineStr"/>
+      <c r="I62" s="5" t="inlineStr"/>
+      <c r="J62" s="5" t="inlineStr"/>
+      <c r="K62" s="5" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
+      <c r="L62" s="5" t="inlineStr"/>
+      <c r="M62" s="5" t="inlineStr"/>
+      <c r="N62" s="5" t="inlineStr"/>
+      <c r="O62" s="5" t="inlineStr">
+        <is>
+          <t>When the row was last changed. Set automatically by trigger trg_&lt;table&gt;_updated_at.</t>
+        </is>
+      </c>
+      <c r="P62" s="5" t="inlineStr">
+        <is>
+          <t>Audit column.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="inlineStr">
-        <is>
-          <t>academic_period</t>
-        </is>
-      </c>
-      <c r="B63" s="5" t="inlineStr">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Rooms or spaces where classes take place.</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="n"/>
+      <c r="D63" s="2" t="n"/>
+      <c r="E63" s="2" t="n"/>
+      <c r="F63" s="2" t="n"/>
+      <c r="G63" s="2" t="n"/>
+      <c r="H63" s="2" t="n"/>
+      <c r="I63" s="2" t="n"/>
+      <c r="J63" s="2" t="n"/>
+      <c r="K63" s="2" t="n"/>
+      <c r="L63" s="2" t="n"/>
+      <c r="M63" s="2" t="n"/>
+      <c r="N63" s="2" t="n"/>
+      <c r="O63" s="2" t="n"/>
+      <c r="P63" s="2" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr"/>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr"/>
+      <c r="G64" s="3" t="inlineStr"/>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>Yes (PK)</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="inlineStr"/>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>IDENTITY</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr"/>
+      <c r="M64" s="3" t="inlineStr"/>
+      <c r="N64" s="3" t="inlineStr"/>
+      <c r="O64" s="3" t="inlineStr">
+        <is>
+          <t>Unique identifier of the location.</t>
+        </is>
+      </c>
+      <c r="P64" s="3" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="inlineStr"/>
+      <c r="F65" s="6" t="inlineStr"/>
+      <c r="G65" s="6" t="inlineStr"/>
+      <c r="H65" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I65" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J65" s="6" t="inlineStr"/>
+      <c r="K65" s="6" t="inlineStr"/>
+      <c r="L65" s="6" t="inlineStr"/>
+      <c r="M65" s="6" t="inlineStr"/>
+      <c r="N65" s="6" t="inlineStr"/>
+      <c r="O65" s="6" t="inlineStr">
+        <is>
+          <t>Location name, e.g. Room 3.02.</t>
+        </is>
+      </c>
+      <c r="P65" s="6" t="inlineStr">
+        <is>
+          <t>Assumption: unique.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>qr_secret_seed</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>BYTEA</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr"/>
+      <c r="E66" s="4" t="inlineStr"/>
+      <c r="F66" s="4" t="inlineStr"/>
+      <c r="G66" s="4" t="inlineStr"/>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J66" s="4" t="inlineStr"/>
+      <c r="K66" s="4" t="inlineStr"/>
+      <c r="L66" s="4" t="inlineStr">
+        <is>
+          <t>octet_length(qr_secret_seed) BETWEEN 16 AND 64</t>
+        </is>
+      </c>
+      <c r="M66" s="4" t="inlineStr"/>
+      <c r="N66" s="4" t="inlineStr"/>
+      <c r="O66" s="4" t="inlineStr">
+        <is>
+          <t>Secret seed used to generate the location's rotating QR code. Stored as raw bytes; shown as hex in the app (encode(qr_secret_seed, 'hex')). NULL = location has no QR check-in.</t>
+        </is>
+      </c>
+      <c r="P66" s="4" t="inlineStr">
+        <is>
+          <t>Sensitive: never expose to clients. Restrict read access or encrypt at rest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="C63" s="5" t="inlineStr">
+      <c r="C67" s="5" t="inlineStr">
         <is>
           <t>TIMESTAMPTZ</t>
         </is>
       </c>
-      <c r="D63" s="5" t="inlineStr"/>
-      <c r="E63" s="5" t="inlineStr"/>
-      <c r="F63" s="5" t="inlineStr"/>
-      <c r="G63" s="5" t="inlineStr"/>
-      <c r="H63" s="5" t="inlineStr">
+      <c r="D67" s="5" t="inlineStr"/>
+      <c r="E67" s="5" t="inlineStr"/>
+      <c r="F67" s="5" t="inlineStr"/>
+      <c r="G67" s="5" t="inlineStr"/>
+      <c r="H67" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I63" s="5" t="inlineStr"/>
-      <c r="J63" s="5" t="inlineStr"/>
-      <c r="K63" s="5" t="inlineStr">
+      <c r="I67" s="5" t="inlineStr"/>
+      <c r="J67" s="5" t="inlineStr"/>
+      <c r="K67" s="5" t="inlineStr">
         <is>
           <t>now()</t>
         </is>
       </c>
-      <c r="L63" s="5" t="inlineStr"/>
-      <c r="M63" s="5" t="inlineStr"/>
-      <c r="N63" s="5" t="inlineStr"/>
-      <c r="O63" s="5" t="inlineStr">
+      <c r="L67" s="5" t="inlineStr"/>
+      <c r="M67" s="5" t="inlineStr"/>
+      <c r="N67" s="5" t="inlineStr"/>
+      <c r="O67" s="5" t="inlineStr">
         <is>
           <t>When the row was created.</t>
         </is>
       </c>
-      <c r="P63" s="5" t="inlineStr">
+      <c r="P67" s="5" t="inlineStr">
         <is>
           <t>Audit column.</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>academic_period</t>
-        </is>
-      </c>
-      <c r="B64" s="5" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="C64" s="5" t="inlineStr">
+      <c r="C68" s="5" t="inlineStr">
         <is>
           <t>TIMESTAMPTZ</t>
         </is>
       </c>
-      <c r="D64" s="5" t="inlineStr"/>
-      <c r="E64" s="5" t="inlineStr"/>
-      <c r="F64" s="5" t="inlineStr"/>
-      <c r="G64" s="5" t="inlineStr"/>
-      <c r="H64" s="5" t="inlineStr">
+      <c r="D68" s="5" t="inlineStr"/>
+      <c r="E68" s="5" t="inlineStr"/>
+      <c r="F68" s="5" t="inlineStr"/>
+      <c r="G68" s="5" t="inlineStr"/>
+      <c r="H68" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I64" s="5" t="inlineStr"/>
-      <c r="J64" s="5" t="inlineStr"/>
-      <c r="K64" s="5" t="inlineStr">
+      <c r="I68" s="5" t="inlineStr"/>
+      <c r="J68" s="5" t="inlineStr"/>
+      <c r="K68" s="5" t="inlineStr">
         <is>
           <t>now()</t>
         </is>
       </c>
-      <c r="L64" s="5" t="inlineStr"/>
-      <c r="M64" s="5" t="inlineStr"/>
-      <c r="N64" s="5" t="inlineStr"/>
-      <c r="O64" s="5" t="inlineStr">
+      <c r="L68" s="5" t="inlineStr"/>
+      <c r="M68" s="5" t="inlineStr"/>
+      <c r="N68" s="5" t="inlineStr"/>
+      <c r="O68" s="5" t="inlineStr">
         <is>
           <t>When the row was last changed. Set automatically by trigger trg_&lt;table&gt;_updated_at.</t>
         </is>
       </c>
-      <c r="P64" s="5" t="inlineStr">
+      <c r="P68" s="5" t="inlineStr">
         <is>
           <t>Audit column.</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>class</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>Subjects or units offered.</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="n"/>
-      <c r="D65" s="2" t="n"/>
-      <c r="E65" s="2" t="n"/>
-      <c r="F65" s="2" t="n"/>
-      <c r="G65" s="2" t="n"/>
-      <c r="H65" s="2" t="n"/>
-      <c r="I65" s="2" t="n"/>
-      <c r="J65" s="2" t="n"/>
-      <c r="K65" s="2" t="n"/>
-      <c r="L65" s="2" t="n"/>
-      <c r="M65" s="2" t="n"/>
-      <c r="N65" s="2" t="n"/>
-      <c r="O65" s="2" t="n"/>
-      <c r="P65" s="2" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="3" t="inlineStr">
-        <is>
-          <t>class</t>
-        </is>
-      </c>
-      <c r="B66" s="3" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>beacon</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Bluetooth (iBeacon) devices used to confirm a student is in the room.</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="n"/>
+      <c r="D69" s="2" t="n"/>
+      <c r="E69" s="2" t="n"/>
+      <c r="F69" s="2" t="n"/>
+      <c r="G69" s="2" t="n"/>
+      <c r="H69" s="2" t="n"/>
+      <c r="I69" s="2" t="n"/>
+      <c r="J69" s="2" t="n"/>
+      <c r="K69" s="2" t="n"/>
+      <c r="L69" s="2" t="n"/>
+      <c r="M69" s="2" t="n"/>
+      <c r="N69" s="2" t="n"/>
+      <c r="O69" s="2" t="n"/>
+      <c r="P69" s="2" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>beacon</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C66" s="3" t="inlineStr">
+      <c r="C70" s="3" t="inlineStr">
         <is>
           <t>INTEGER</t>
         </is>
       </c>
-      <c r="D66" s="3" t="inlineStr"/>
-      <c r="E66" s="3" t="inlineStr">
+      <c r="D70" s="3" t="inlineStr"/>
+      <c r="E70" s="3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F66" s="3" t="inlineStr"/>
-      <c r="G66" s="3" t="inlineStr"/>
-      <c r="H66" s="3" t="inlineStr">
+      <c r="F70" s="3" t="inlineStr"/>
+      <c r="G70" s="3" t="inlineStr"/>
+      <c r="H70" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I66" s="3" t="inlineStr">
+      <c r="I70" s="3" t="inlineStr">
         <is>
           <t>Yes (PK)</t>
         </is>
       </c>
-      <c r="J66" s="3" t="inlineStr"/>
-      <c r="K66" s="3" t="inlineStr">
+      <c r="J70" s="3" t="inlineStr"/>
+      <c r="K70" s="3" t="inlineStr">
         <is>
           <t>IDENTITY</t>
         </is>
       </c>
-      <c r="L66" s="3" t="inlineStr"/>
-      <c r="M66" s="3" t="inlineStr"/>
-      <c r="N66" s="3" t="inlineStr"/>
-      <c r="O66" s="3" t="inlineStr">
-        <is>
-          <t>Unique identifier of the class.</t>
-        </is>
-      </c>
-      <c r="P66" s="3" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="4" t="inlineStr">
-        <is>
-          <t>class</t>
-        </is>
-      </c>
-      <c r="B67" s="4" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C67" s="4" t="inlineStr">
-        <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="D67" s="4" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="E67" s="4" t="inlineStr"/>
-      <c r="F67" s="4" t="inlineStr"/>
-      <c r="G67" s="4" t="inlineStr"/>
-      <c r="H67" s="4" t="inlineStr">
+      <c r="L70" s="3" t="inlineStr"/>
+      <c r="M70" s="3" t="inlineStr"/>
+      <c r="N70" s="3" t="inlineStr"/>
+      <c r="O70" s="3" t="inlineStr">
+        <is>
+          <t>Unique identifier of the beacon.</t>
+        </is>
+      </c>
+      <c r="P70" s="3" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>beacon</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>location_id</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr"/>
+      <c r="E71" s="4" t="inlineStr"/>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="inlineStr">
+        <is>
+          <t>location.id</t>
+        </is>
+      </c>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I71" s="4" t="inlineStr"/>
+      <c r="J71" s="4" t="inlineStr"/>
+      <c r="K71" s="4" t="inlineStr"/>
+      <c r="L71" s="4" t="inlineStr"/>
+      <c r="M71" s="4" t="inlineStr">
+        <is>
+          <t>SET NULL</t>
+        </is>
+      </c>
+      <c r="N71" s="4" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
+      <c r="O71" s="4" t="inlineStr">
+        <is>
+          <t>Location the beacon is installed in. NULL when not assigned.</t>
+        </is>
+      </c>
+      <c r="P71" s="4" t="inlineStr">
+        <is>
+          <t>Confirmed nullable. SET NULL keeps the beacon if its location is deleted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>beacon</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>UUID</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr"/>
+      <c r="E72" s="4" t="inlineStr"/>
+      <c r="F72" s="4" t="inlineStr"/>
+      <c r="G72" s="4" t="inlineStr"/>
+      <c r="H72" s="4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I67" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J67" s="4" t="inlineStr"/>
-      <c r="K67" s="4" t="inlineStr"/>
-      <c r="L67" s="4" t="inlineStr"/>
-      <c r="M67" s="4" t="inlineStr"/>
-      <c r="N67" s="4" t="inlineStr"/>
-      <c r="O67" s="4" t="inlineStr">
-        <is>
-          <t>Class name.</t>
-        </is>
-      </c>
-      <c r="P67" s="4" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="4" t="inlineStr">
-        <is>
-          <t>class</t>
-        </is>
-      </c>
-      <c r="B68" s="4" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C68" s="4" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="D68" s="4" t="inlineStr"/>
-      <c r="E68" s="4" t="inlineStr"/>
-      <c r="F68" s="4" t="inlineStr"/>
-      <c r="G68" s="4" t="inlineStr"/>
-      <c r="H68" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I68" s="4" t="inlineStr"/>
-      <c r="J68" s="4" t="inlineStr"/>
-      <c r="K68" s="4" t="inlineStr"/>
-      <c r="L68" s="4" t="inlineStr"/>
-      <c r="M68" s="4" t="inlineStr"/>
-      <c r="N68" s="4" t="inlineStr"/>
-      <c r="O68" s="4" t="inlineStr">
-        <is>
-          <t>Class description.</t>
-        </is>
-      </c>
-      <c r="P68" s="4" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="5" t="inlineStr">
-        <is>
-          <t>class</t>
-        </is>
-      </c>
-      <c r="B69" s="5" t="inlineStr">
-        <is>
-          <t>created_at</t>
-        </is>
-      </c>
-      <c r="C69" s="5" t="inlineStr">
-        <is>
-          <t>TIMESTAMPTZ</t>
-        </is>
-      </c>
-      <c r="D69" s="5" t="inlineStr"/>
-      <c r="E69" s="5" t="inlineStr"/>
-      <c r="F69" s="5" t="inlineStr"/>
-      <c r="G69" s="5" t="inlineStr"/>
-      <c r="H69" s="5" t="inlineStr">
+      <c r="I72" s="4" t="inlineStr"/>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>uq_beacon_identity</t>
+        </is>
+      </c>
+      <c r="K72" s="4" t="inlineStr"/>
+      <c r="L72" s="4" t="inlineStr"/>
+      <c r="M72" s="4" t="inlineStr"/>
+      <c r="N72" s="4" t="inlineStr"/>
+      <c r="O72" s="4" t="inlineStr">
+        <is>
+          <t>iBeacon proximity UUID.</t>
+        </is>
+      </c>
+      <c r="P72" s="4" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>beacon</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr"/>
+      <c r="E73" s="4" t="inlineStr"/>
+      <c r="F73" s="4" t="inlineStr"/>
+      <c r="G73" s="4" t="inlineStr"/>
+      <c r="H73" s="4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I69" s="5" t="inlineStr"/>
-      <c r="J69" s="5" t="inlineStr"/>
-      <c r="K69" s="5" t="inlineStr">
-        <is>
-          <t>now()</t>
-        </is>
-      </c>
-      <c r="L69" s="5" t="inlineStr"/>
-      <c r="M69" s="5" t="inlineStr"/>
-      <c r="N69" s="5" t="inlineStr"/>
-      <c r="O69" s="5" t="inlineStr">
-        <is>
-          <t>When the row was created.</t>
-        </is>
-      </c>
-      <c r="P69" s="5" t="inlineStr">
-        <is>
-          <t>Audit column.</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>class</t>
-        </is>
-      </c>
-      <c r="B70" s="5" t="inlineStr">
-        <is>
-          <t>updated_at</t>
-        </is>
-      </c>
-      <c r="C70" s="5" t="inlineStr">
-        <is>
-          <t>TIMESTAMPTZ</t>
-        </is>
-      </c>
-      <c r="D70" s="5" t="inlineStr"/>
-      <c r="E70" s="5" t="inlineStr"/>
-      <c r="F70" s="5" t="inlineStr"/>
-      <c r="G70" s="5" t="inlineStr"/>
-      <c r="H70" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I70" s="5" t="inlineStr"/>
-      <c r="J70" s="5" t="inlineStr"/>
-      <c r="K70" s="5" t="inlineStr">
-        <is>
-          <t>now()</t>
-        </is>
-      </c>
-      <c r="L70" s="5" t="inlineStr"/>
-      <c r="M70" s="5" t="inlineStr"/>
-      <c r="N70" s="5" t="inlineStr"/>
-      <c r="O70" s="5" t="inlineStr">
-        <is>
-          <t>When the row was last changed. Set automatically by trigger trg_&lt;table&gt;_updated_at.</t>
-        </is>
-      </c>
-      <c r="P70" s="5" t="inlineStr">
-        <is>
-          <t>Audit column.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>Rooms or spaces where classes take place.</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="n"/>
-      <c r="D71" s="2" t="n"/>
-      <c r="E71" s="2" t="n"/>
-      <c r="F71" s="2" t="n"/>
-      <c r="G71" s="2" t="n"/>
-      <c r="H71" s="2" t="n"/>
-      <c r="I71" s="2" t="n"/>
-      <c r="J71" s="2" t="n"/>
-      <c r="K71" s="2" t="n"/>
-      <c r="L71" s="2" t="n"/>
-      <c r="M71" s="2" t="n"/>
-      <c r="N71" s="2" t="n"/>
-      <c r="O71" s="2" t="n"/>
-      <c r="P71" s="2" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="3" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="B72" s="3" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="C72" s="3" t="inlineStr">
-        <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="D72" s="3" t="inlineStr"/>
-      <c r="E72" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F72" s="3" t="inlineStr"/>
-      <c r="G72" s="3" t="inlineStr"/>
-      <c r="H72" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I72" s="3" t="inlineStr">
-        <is>
-          <t>Yes (PK)</t>
-        </is>
-      </c>
-      <c r="J72" s="3" t="inlineStr"/>
-      <c r="K72" s="3" t="inlineStr">
-        <is>
-          <t>IDENTITY</t>
-        </is>
-      </c>
-      <c r="L72" s="3" t="inlineStr"/>
-      <c r="M72" s="3" t="inlineStr"/>
-      <c r="N72" s="3" t="inlineStr"/>
-      <c r="O72" s="3" t="inlineStr">
-        <is>
-          <t>Unique identifier of the location.</t>
-        </is>
-      </c>
-      <c r="P72" s="3" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="6" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="B73" s="6" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C73" s="6" t="inlineStr">
-        <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="D73" s="6" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E73" s="6" t="inlineStr"/>
-      <c r="F73" s="6" t="inlineStr"/>
-      <c r="G73" s="6" t="inlineStr"/>
-      <c r="H73" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I73" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J73" s="6" t="inlineStr"/>
-      <c r="K73" s="6" t="inlineStr"/>
-      <c r="L73" s="6" t="inlineStr"/>
-      <c r="M73" s="6" t="inlineStr"/>
-      <c r="N73" s="6" t="inlineStr"/>
-      <c r="O73" s="6" t="inlineStr">
-        <is>
-          <t>Location name, e.g. Room 3.02.</t>
-        </is>
-      </c>
-      <c r="P73" s="6" t="inlineStr">
-        <is>
-          <t>Assumption: unique.</t>
+      <c r="I73" s="4" t="inlineStr"/>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>uq_beacon_identity</t>
+        </is>
+      </c>
+      <c r="K73" s="4" t="inlineStr"/>
+      <c r="L73" s="4" t="inlineStr">
+        <is>
+          <t>major BETWEEN 0 AND 65535</t>
+        </is>
+      </c>
+      <c r="M73" s="4" t="inlineStr"/>
+      <c r="N73" s="4" t="inlineStr"/>
+      <c r="O73" s="4" t="inlineStr">
+        <is>
+          <t>iBeacon major value (0 to 65535).</t>
+        </is>
+      </c>
+      <c r="P73" s="4" t="inlineStr">
+        <is>
+          <t>INTEGER because SMALLINT max is 32767.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>beacon</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>qr_secret_seed</t>
+          <t>minor</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>BYTEA</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr"/>
@@ -3870,89 +3910,81 @@
       <c r="G74" s="4" t="inlineStr"/>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I74" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J74" s="4" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I74" s="4" t="inlineStr"/>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>uq_beacon_identity</t>
+        </is>
+      </c>
       <c r="K74" s="4" t="inlineStr"/>
       <c r="L74" s="4" t="inlineStr">
         <is>
-          <t>octet_length(qr_secret_seed) BETWEEN 16 AND 64</t>
+          <t>minor BETWEEN 0 AND 65535</t>
         </is>
       </c>
       <c r="M74" s="4" t="inlineStr"/>
       <c r="N74" s="4" t="inlineStr"/>
       <c r="O74" s="4" t="inlineStr">
         <is>
-          <t>Secret seed used to generate the location's rotating QR code. Stored as raw bytes; shown as hex in the app (encode(qr_secret_seed, 'hex')). NULL = location has no QR check-in.</t>
-        </is>
-      </c>
-      <c r="P74" s="4" t="inlineStr">
-        <is>
-          <t>Sensitive: never expose to clients. Restrict read access or encrypt at rest.</t>
-        </is>
-      </c>
+          <t>iBeacon minor value (0 to 65535).</t>
+        </is>
+      </c>
+      <c r="P74" s="4" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="5" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="B75" s="5" t="inlineStr">
-        <is>
-          <t>created_at</t>
-        </is>
-      </c>
-      <c r="C75" s="5" t="inlineStr">
-        <is>
-          <t>TIMESTAMPTZ</t>
-        </is>
-      </c>
-      <c r="D75" s="5" t="inlineStr"/>
-      <c r="E75" s="5" t="inlineStr"/>
-      <c r="F75" s="5" t="inlineStr"/>
-      <c r="G75" s="5" t="inlineStr"/>
-      <c r="H75" s="5" t="inlineStr">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>beacon</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>rssi_calibrated</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>SMALLINT</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr"/>
+      <c r="E75" s="4" t="inlineStr"/>
+      <c r="F75" s="4" t="inlineStr"/>
+      <c r="G75" s="4" t="inlineStr"/>
+      <c r="H75" s="4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I75" s="5" t="inlineStr"/>
-      <c r="J75" s="5" t="inlineStr"/>
-      <c r="K75" s="5" t="inlineStr">
-        <is>
-          <t>now()</t>
-        </is>
-      </c>
-      <c r="L75" s="5" t="inlineStr"/>
-      <c r="M75" s="5" t="inlineStr"/>
-      <c r="N75" s="5" t="inlineStr"/>
-      <c r="O75" s="5" t="inlineStr">
-        <is>
-          <t>When the row was created.</t>
-        </is>
-      </c>
-      <c r="P75" s="5" t="inlineStr">
-        <is>
-          <t>Audit column.</t>
-        </is>
-      </c>
+      <c r="I75" s="4" t="inlineStr"/>
+      <c r="J75" s="4" t="inlineStr"/>
+      <c r="K75" s="4" t="inlineStr"/>
+      <c r="L75" s="4" t="inlineStr">
+        <is>
+          <t>rssi_calibrated BETWEEN -127 AND 0</t>
+        </is>
+      </c>
+      <c r="M75" s="4" t="inlineStr"/>
+      <c r="N75" s="4" t="inlineStr"/>
+      <c r="O75" s="4" t="inlineStr">
+        <is>
+          <t>Measured power in dBm at 1 metre (usually around -59), used to estimate distance.</t>
+        </is>
+      </c>
+      <c r="P75" s="4" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>beacon</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
@@ -3981,208 +4013,224 @@
       <c r="N76" s="5" t="inlineStr"/>
       <c r="O76" s="5" t="inlineStr">
         <is>
+          <t>When the row was created.</t>
+        </is>
+      </c>
+      <c r="P76" s="5" t="inlineStr">
+        <is>
+          <t>Audit column.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>beacon</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>TIMESTAMPTZ</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr"/>
+      <c r="E77" s="5" t="inlineStr"/>
+      <c r="F77" s="5" t="inlineStr"/>
+      <c r="G77" s="5" t="inlineStr"/>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I77" s="5" t="inlineStr"/>
+      <c r="J77" s="5" t="inlineStr"/>
+      <c r="K77" s="5" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
+      <c r="L77" s="5" t="inlineStr"/>
+      <c r="M77" s="5" t="inlineStr"/>
+      <c r="N77" s="5" t="inlineStr"/>
+      <c r="O77" s="5" t="inlineStr">
+        <is>
           <t>When the row was last changed. Set automatically by trigger trg_&lt;table&gt;_updated_at.</t>
         </is>
       </c>
-      <c r="P76" s="5" t="inlineStr">
+      <c r="P77" s="5" t="inlineStr">
         <is>
           <t>Audit column.</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>beacon</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>Bluetooth (iBeacon) devices used to confirm a student is in the room.</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="n"/>
-      <c r="D77" s="2" t="n"/>
-      <c r="E77" s="2" t="n"/>
-      <c r="F77" s="2" t="n"/>
-      <c r="G77" s="2" t="n"/>
-      <c r="H77" s="2" t="n"/>
-      <c r="I77" s="2" t="n"/>
-      <c r="J77" s="2" t="n"/>
-      <c r="K77" s="2" t="n"/>
-      <c r="L77" s="2" t="n"/>
-      <c r="M77" s="2" t="n"/>
-      <c r="N77" s="2" t="n"/>
-      <c r="O77" s="2" t="n"/>
-      <c r="P77" s="2" t="n"/>
-    </row>
     <row r="78">
-      <c r="A78" s="3" t="inlineStr">
-        <is>
-          <t>beacon</t>
-        </is>
-      </c>
-      <c r="B78" s="3" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="C78" s="3" t="inlineStr">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>nfc_tags</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>NFC tags placed in locations that students tap to check in.</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="n"/>
+      <c r="D78" s="2" t="n"/>
+      <c r="E78" s="2" t="n"/>
+      <c r="F78" s="2" t="n"/>
+      <c r="G78" s="2" t="n"/>
+      <c r="H78" s="2" t="n"/>
+      <c r="I78" s="2" t="n"/>
+      <c r="J78" s="2" t="n"/>
+      <c r="K78" s="2" t="n"/>
+      <c r="L78" s="2" t="n"/>
+      <c r="M78" s="2" t="n"/>
+      <c r="N78" s="2" t="n"/>
+      <c r="O78" s="2" t="n"/>
+      <c r="P78" s="2" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>nfc_tags</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>nfc_uid</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="inlineStr"/>
+      <c r="G79" s="3" t="inlineStr"/>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I79" s="3" t="inlineStr">
+        <is>
+          <t>Yes (PK)</t>
+        </is>
+      </c>
+      <c r="J79" s="3" t="inlineStr"/>
+      <c r="K79" s="3" t="inlineStr"/>
+      <c r="L79" s="3" t="inlineStr">
+        <is>
+          <t>nfc_uid ~ '^[0-9A-F]{8}([0-9A-F]{6}){0,2}$'</t>
+        </is>
+      </c>
+      <c r="M79" s="3" t="inlineStr"/>
+      <c r="N79" s="3" t="inlineStr"/>
+      <c r="O79" s="3" t="inlineStr">
+        <is>
+          <t>Hardware UID of the tag as uppercase hex: 4, 7 or 10 bytes (8, 14 or 20 hex characters).</t>
+        </is>
+      </c>
+      <c r="P79" s="3" t="inlineStr">
+        <is>
+          <t>Natural key from the tag itself. The app should uppercase the UID before saving.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>nfc_tags</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>location_id</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
         <is>
           <t>INTEGER</t>
         </is>
       </c>
-      <c r="D78" s="3" t="inlineStr"/>
-      <c r="E78" s="3" t="inlineStr">
+      <c r="D80" s="6" t="inlineStr"/>
+      <c r="E80" s="6" t="inlineStr"/>
+      <c r="F80" s="6" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F78" s="3" t="inlineStr"/>
-      <c r="G78" s="3" t="inlineStr"/>
-      <c r="H78" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I78" s="3" t="inlineStr">
-        <is>
-          <t>Yes (PK)</t>
-        </is>
-      </c>
-      <c r="J78" s="3" t="inlineStr"/>
-      <c r="K78" s="3" t="inlineStr">
-        <is>
-          <t>IDENTITY</t>
-        </is>
-      </c>
-      <c r="L78" s="3" t="inlineStr"/>
-      <c r="M78" s="3" t="inlineStr"/>
-      <c r="N78" s="3" t="inlineStr"/>
-      <c r="O78" s="3" t="inlineStr">
-        <is>
-          <t>Unique identifier of the beacon.</t>
-        </is>
-      </c>
-      <c r="P78" s="3" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="4" t="inlineStr">
-        <is>
-          <t>beacon</t>
-        </is>
-      </c>
-      <c r="B79" s="4" t="inlineStr">
-        <is>
-          <t>location_id</t>
-        </is>
-      </c>
-      <c r="C79" s="4" t="inlineStr">
-        <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="D79" s="4" t="inlineStr"/>
-      <c r="E79" s="4" t="inlineStr"/>
-      <c r="F79" s="4" t="inlineStr">
+      <c r="G80" s="6" t="inlineStr">
+        <is>
+          <t>location.id</t>
+        </is>
+      </c>
+      <c r="H80" s="6" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G79" s="4" t="inlineStr">
-        <is>
-          <t>location.id</t>
-        </is>
-      </c>
-      <c r="H79" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I79" s="4" t="inlineStr"/>
-      <c r="J79" s="4" t="inlineStr"/>
-      <c r="K79" s="4" t="inlineStr"/>
-      <c r="L79" s="4" t="inlineStr"/>
-      <c r="M79" s="4" t="inlineStr">
+      <c r="I80" s="6" t="inlineStr"/>
+      <c r="J80" s="6" t="inlineStr"/>
+      <c r="K80" s="6" t="inlineStr"/>
+      <c r="L80" s="6" t="inlineStr"/>
+      <c r="M80" s="6" t="inlineStr">
         <is>
           <t>SET NULL</t>
         </is>
       </c>
-      <c r="N79" s="4" t="inlineStr">
+      <c r="N80" s="6" t="inlineStr">
         <is>
           <t>NO ACTION</t>
         </is>
       </c>
-      <c r="O79" s="4" t="inlineStr">
-        <is>
-          <t>Location the beacon is installed in. NULL when not assigned.</t>
-        </is>
-      </c>
-      <c r="P79" s="4" t="inlineStr">
-        <is>
-          <t>Confirmed nullable. SET NULL keeps the beacon if its location is deleted.</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="4" t="inlineStr">
-        <is>
-          <t>beacon</t>
-        </is>
-      </c>
-      <c r="B80" s="4" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="C80" s="4" t="inlineStr">
-        <is>
-          <t>UUID</t>
-        </is>
-      </c>
-      <c r="D80" s="4" t="inlineStr"/>
-      <c r="E80" s="4" t="inlineStr"/>
-      <c r="F80" s="4" t="inlineStr"/>
-      <c r="G80" s="4" t="inlineStr"/>
-      <c r="H80" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I80" s="4" t="inlineStr"/>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>uq_beacon_identity</t>
-        </is>
-      </c>
-      <c r="K80" s="4" t="inlineStr"/>
-      <c r="L80" s="4" t="inlineStr"/>
-      <c r="M80" s="4" t="inlineStr"/>
-      <c r="N80" s="4" t="inlineStr"/>
-      <c r="O80" s="4" t="inlineStr">
-        <is>
-          <t>iBeacon proximity UUID.</t>
-        </is>
-      </c>
-      <c r="P80" s="4" t="inlineStr"/>
+      <c r="O80" s="6" t="inlineStr">
+        <is>
+          <t>Location the tag is installed in. NULL when not assigned.</t>
+        </is>
+      </c>
+      <c r="P80" s="6" t="inlineStr">
+        <is>
+          <t>Assumption: nullable, same as beacon.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>beacon</t>
+          <t>nfc_tags</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>major</t>
+          <t>payload_token</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="D81" s="4" t="inlineStr"/>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
       <c r="E81" s="4" t="inlineStr"/>
       <c r="F81" s="4" t="inlineStr"/>
       <c r="G81" s="4" t="inlineStr"/>
@@ -4191,362 +4239,370 @@
           <t>No</t>
         </is>
       </c>
-      <c r="I81" s="4" t="inlineStr"/>
-      <c r="J81" s="4" t="inlineStr">
-        <is>
-          <t>uq_beacon_identity</t>
-        </is>
-      </c>
+      <c r="I81" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J81" s="4" t="inlineStr"/>
       <c r="K81" s="4" t="inlineStr"/>
-      <c r="L81" s="4" t="inlineStr">
-        <is>
-          <t>major BETWEEN 0 AND 65535</t>
-        </is>
-      </c>
+      <c r="L81" s="4" t="inlineStr"/>
       <c r="M81" s="4" t="inlineStr"/>
       <c r="N81" s="4" t="inlineStr"/>
       <c r="O81" s="4" t="inlineStr">
         <is>
-          <t>iBeacon major value (0 to 65535).</t>
-        </is>
-      </c>
-      <c r="P81" s="4" t="inlineStr">
-        <is>
-          <t>INTEGER because SMALLINT max is 32767.</t>
-        </is>
-      </c>
+          <t>Token written to the tag and validated by the server on tap.</t>
+        </is>
+      </c>
+      <c r="P81" s="4" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="4" t="inlineStr">
-        <is>
-          <t>beacon</t>
-        </is>
-      </c>
-      <c r="B82" s="4" t="inlineStr">
-        <is>
-          <t>minor</t>
-        </is>
-      </c>
-      <c r="C82" s="4" t="inlineStr">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>nfc_tags</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>TIMESTAMPTZ</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr"/>
+      <c r="E82" s="5" t="inlineStr"/>
+      <c r="F82" s="5" t="inlineStr"/>
+      <c r="G82" s="5" t="inlineStr"/>
+      <c r="H82" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I82" s="5" t="inlineStr"/>
+      <c r="J82" s="5" t="inlineStr"/>
+      <c r="K82" s="5" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
+      <c r="L82" s="5" t="inlineStr"/>
+      <c r="M82" s="5" t="inlineStr"/>
+      <c r="N82" s="5" t="inlineStr"/>
+      <c r="O82" s="5" t="inlineStr">
+        <is>
+          <t>When the row was created.</t>
+        </is>
+      </c>
+      <c r="P82" s="5" t="inlineStr">
+        <is>
+          <t>Audit column.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>nfc_tags</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>TIMESTAMPTZ</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr"/>
+      <c r="E83" s="5" t="inlineStr"/>
+      <c r="F83" s="5" t="inlineStr"/>
+      <c r="G83" s="5" t="inlineStr"/>
+      <c r="H83" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I83" s="5" t="inlineStr"/>
+      <c r="J83" s="5" t="inlineStr"/>
+      <c r="K83" s="5" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
+      <c r="L83" s="5" t="inlineStr"/>
+      <c r="M83" s="5" t="inlineStr"/>
+      <c r="N83" s="5" t="inlineStr"/>
+      <c r="O83" s="5" t="inlineStr">
+        <is>
+          <t>When the row was last changed. Set automatically by trigger trg_&lt;table&gt;_updated_at.</t>
+        </is>
+      </c>
+      <c r="P83" s="5" t="inlineStr">
+        <is>
+          <t>Audit column.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>class_schedule</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Recurring timetable slot for a class in a period.</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="n"/>
+      <c r="D84" s="2" t="n"/>
+      <c r="E84" s="2" t="n"/>
+      <c r="F84" s="2" t="n"/>
+      <c r="G84" s="2" t="n"/>
+      <c r="H84" s="2" t="n"/>
+      <c r="I84" s="2" t="n"/>
+      <c r="J84" s="2" t="n"/>
+      <c r="K84" s="2" t="n"/>
+      <c r="L84" s="2" t="n"/>
+      <c r="M84" s="2" t="n"/>
+      <c r="N84" s="2" t="n"/>
+      <c r="O84" s="2" t="n"/>
+      <c r="P84" s="2" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>class_schedule</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
         <is>
           <t>INTEGER</t>
         </is>
       </c>
-      <c r="D82" s="4" t="inlineStr"/>
-      <c r="E82" s="4" t="inlineStr"/>
-      <c r="F82" s="4" t="inlineStr"/>
-      <c r="G82" s="4" t="inlineStr"/>
-      <c r="H82" s="4" t="inlineStr">
+      <c r="D85" s="3" t="inlineStr"/>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="inlineStr"/>
+      <c r="G85" s="3" t="inlineStr"/>
+      <c r="H85" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I82" s="4" t="inlineStr"/>
-      <c r="J82" s="4" t="inlineStr">
-        <is>
-          <t>uq_beacon_identity</t>
-        </is>
-      </c>
-      <c r="K82" s="4" t="inlineStr"/>
-      <c r="L82" s="4" t="inlineStr">
-        <is>
-          <t>minor BETWEEN 0 AND 65535</t>
-        </is>
-      </c>
-      <c r="M82" s="4" t="inlineStr"/>
-      <c r="N82" s="4" t="inlineStr"/>
-      <c r="O82" s="4" t="inlineStr">
-        <is>
-          <t>iBeacon minor value (0 to 65535).</t>
-        </is>
-      </c>
-      <c r="P82" s="4" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="4" t="inlineStr">
-        <is>
-          <t>beacon</t>
-        </is>
-      </c>
-      <c r="B83" s="4" t="inlineStr">
-        <is>
-          <t>rssi_calibrated</t>
-        </is>
-      </c>
-      <c r="C83" s="4" t="inlineStr">
-        <is>
-          <t>SMALLINT</t>
-        </is>
-      </c>
-      <c r="D83" s="4" t="inlineStr"/>
-      <c r="E83" s="4" t="inlineStr"/>
-      <c r="F83" s="4" t="inlineStr"/>
-      <c r="G83" s="4" t="inlineStr"/>
-      <c r="H83" s="4" t="inlineStr">
+      <c r="I85" s="3" t="inlineStr">
+        <is>
+          <t>Yes (PK)</t>
+        </is>
+      </c>
+      <c r="J85" s="3" t="inlineStr"/>
+      <c r="K85" s="3" t="inlineStr">
+        <is>
+          <t>IDENTITY</t>
+        </is>
+      </c>
+      <c r="L85" s="3" t="inlineStr"/>
+      <c r="M85" s="3" t="inlineStr"/>
+      <c r="N85" s="3" t="inlineStr"/>
+      <c r="O85" s="3" t="inlineStr">
+        <is>
+          <t>Unique identifier of the schedule.</t>
+        </is>
+      </c>
+      <c r="P85" s="3" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>class_schedule</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>class_id</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr"/>
+      <c r="E86" s="4" t="inlineStr"/>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G86" s="4" t="inlineStr">
+        <is>
+          <t>class.id</t>
+        </is>
+      </c>
+      <c r="H86" s="4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I83" s="4" t="inlineStr"/>
-      <c r="J83" s="4" t="inlineStr"/>
-      <c r="K83" s="4" t="inlineStr"/>
-      <c r="L83" s="4" t="inlineStr">
-        <is>
-          <t>rssi_calibrated BETWEEN -127 AND 0</t>
-        </is>
-      </c>
-      <c r="M83" s="4" t="inlineStr"/>
-      <c r="N83" s="4" t="inlineStr"/>
-      <c r="O83" s="4" t="inlineStr">
-        <is>
-          <t>Measured power in dBm at 1 metre (usually around -59), used to estimate distance.</t>
-        </is>
-      </c>
-      <c r="P83" s="4" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="5" t="inlineStr">
-        <is>
-          <t>beacon</t>
-        </is>
-      </c>
-      <c r="B84" s="5" t="inlineStr">
-        <is>
-          <t>created_at</t>
-        </is>
-      </c>
-      <c r="C84" s="5" t="inlineStr">
-        <is>
-          <t>TIMESTAMPTZ</t>
-        </is>
-      </c>
-      <c r="D84" s="5" t="inlineStr"/>
-      <c r="E84" s="5" t="inlineStr"/>
-      <c r="F84" s="5" t="inlineStr"/>
-      <c r="G84" s="5" t="inlineStr"/>
-      <c r="H84" s="5" t="inlineStr">
+      <c r="I86" s="4" t="inlineStr"/>
+      <c r="J86" s="4" t="inlineStr"/>
+      <c r="K86" s="4" t="inlineStr"/>
+      <c r="L86" s="4" t="inlineStr"/>
+      <c r="M86" s="4" t="inlineStr">
+        <is>
+          <t>RESTRICT</t>
+        </is>
+      </c>
+      <c r="N86" s="4" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
+      <c r="O86" s="4" t="inlineStr">
+        <is>
+          <t>Class being taught.</t>
+        </is>
+      </c>
+      <c r="P86" s="4" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>class_schedule</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>academic_period_id</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr"/>
+      <c r="E87" s="4" t="inlineStr"/>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G87" s="4" t="inlineStr">
+        <is>
+          <t>academic_period.id</t>
+        </is>
+      </c>
+      <c r="H87" s="4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I84" s="5" t="inlineStr"/>
-      <c r="J84" s="5" t="inlineStr"/>
-      <c r="K84" s="5" t="inlineStr">
-        <is>
-          <t>now()</t>
-        </is>
-      </c>
-      <c r="L84" s="5" t="inlineStr"/>
-      <c r="M84" s="5" t="inlineStr"/>
-      <c r="N84" s="5" t="inlineStr"/>
-      <c r="O84" s="5" t="inlineStr">
-        <is>
-          <t>When the row was created.</t>
-        </is>
-      </c>
-      <c r="P84" s="5" t="inlineStr">
-        <is>
-          <t>Audit column.</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="5" t="inlineStr">
-        <is>
-          <t>beacon</t>
-        </is>
-      </c>
-      <c r="B85" s="5" t="inlineStr">
-        <is>
-          <t>updated_at</t>
-        </is>
-      </c>
-      <c r="C85" s="5" t="inlineStr">
-        <is>
-          <t>TIMESTAMPTZ</t>
-        </is>
-      </c>
-      <c r="D85" s="5" t="inlineStr"/>
-      <c r="E85" s="5" t="inlineStr"/>
-      <c r="F85" s="5" t="inlineStr"/>
-      <c r="G85" s="5" t="inlineStr"/>
-      <c r="H85" s="5" t="inlineStr">
+      <c r="I87" s="4" t="inlineStr"/>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>uq_schedule_location_slot, uq_schedule_lecturer_slot</t>
+        </is>
+      </c>
+      <c r="K87" s="4" t="inlineStr"/>
+      <c r="L87" s="4" t="inlineStr"/>
+      <c r="M87" s="4" t="inlineStr">
+        <is>
+          <t>RESTRICT</t>
+        </is>
+      </c>
+      <c r="N87" s="4" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
+      <c r="O87" s="4" t="inlineStr">
+        <is>
+          <t>Period the schedule runs in.</t>
+        </is>
+      </c>
+      <c r="P87" s="4" t="inlineStr">
+        <is>
+          <t>Renamed from ERD 'periodId' for clarity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>class_schedule</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>frequency_id</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="inlineStr"/>
+      <c r="E88" s="4" t="inlineStr"/>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G88" s="4" t="inlineStr">
+        <is>
+          <t>frequency.id</t>
+        </is>
+      </c>
+      <c r="H88" s="4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I85" s="5" t="inlineStr"/>
-      <c r="J85" s="5" t="inlineStr"/>
-      <c r="K85" s="5" t="inlineStr">
-        <is>
-          <t>now()</t>
-        </is>
-      </c>
-      <c r="L85" s="5" t="inlineStr"/>
-      <c r="M85" s="5" t="inlineStr"/>
-      <c r="N85" s="5" t="inlineStr"/>
-      <c r="O85" s="5" t="inlineStr">
-        <is>
-          <t>When the row was last changed. Set automatically by trigger trg_&lt;table&gt;_updated_at.</t>
-        </is>
-      </c>
-      <c r="P85" s="5" t="inlineStr">
-        <is>
-          <t>Audit column.</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>nfc_tags</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>NFC tags placed in locations that students tap to check in.</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="n"/>
-      <c r="D86" s="2" t="n"/>
-      <c r="E86" s="2" t="n"/>
-      <c r="F86" s="2" t="n"/>
-      <c r="G86" s="2" t="n"/>
-      <c r="H86" s="2" t="n"/>
-      <c r="I86" s="2" t="n"/>
-      <c r="J86" s="2" t="n"/>
-      <c r="K86" s="2" t="n"/>
-      <c r="L86" s="2" t="n"/>
-      <c r="M86" s="2" t="n"/>
-      <c r="N86" s="2" t="n"/>
-      <c r="O86" s="2" t="n"/>
-      <c r="P86" s="2" t="n"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="3" t="inlineStr">
-        <is>
-          <t>nfc_tags</t>
-        </is>
-      </c>
-      <c r="B87" s="3" t="inlineStr">
-        <is>
-          <t>nfc_uid</t>
-        </is>
-      </c>
-      <c r="C87" s="3" t="inlineStr">
-        <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="D87" s="3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E87" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F87" s="3" t="inlineStr"/>
-      <c r="G87" s="3" t="inlineStr"/>
-      <c r="H87" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I87" s="3" t="inlineStr">
-        <is>
-          <t>Yes (PK)</t>
-        </is>
-      </c>
-      <c r="J87" s="3" t="inlineStr"/>
-      <c r="K87" s="3" t="inlineStr"/>
-      <c r="L87" s="3" t="inlineStr">
-        <is>
-          <t>nfc_uid ~ '^[0-9A-F]{8}([0-9A-F]{6}){0,2}$'</t>
-        </is>
-      </c>
-      <c r="M87" s="3" t="inlineStr"/>
-      <c r="N87" s="3" t="inlineStr"/>
-      <c r="O87" s="3" t="inlineStr">
-        <is>
-          <t>Hardware UID of the tag as uppercase hex: 4, 7 or 10 bytes (8, 14 or 20 hex characters).</t>
-        </is>
-      </c>
-      <c r="P87" s="3" t="inlineStr">
-        <is>
-          <t>Natural key from the tag itself. The app should uppercase the UID before saving.</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="6" t="inlineStr">
-        <is>
-          <t>nfc_tags</t>
-        </is>
-      </c>
-      <c r="B88" s="6" t="inlineStr">
-        <is>
-          <t>location_id</t>
-        </is>
-      </c>
-      <c r="C88" s="6" t="inlineStr">
-        <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="D88" s="6" t="inlineStr"/>
-      <c r="E88" s="6" t="inlineStr"/>
-      <c r="F88" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G88" s="6" t="inlineStr">
-        <is>
-          <t>location.id</t>
-        </is>
-      </c>
-      <c r="H88" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I88" s="6" t="inlineStr"/>
-      <c r="J88" s="6" t="inlineStr"/>
-      <c r="K88" s="6" t="inlineStr"/>
-      <c r="L88" s="6" t="inlineStr"/>
-      <c r="M88" s="6" t="inlineStr">
-        <is>
-          <t>SET NULL</t>
-        </is>
-      </c>
-      <c r="N88" s="6" t="inlineStr">
+      <c r="I88" s="4" t="inlineStr"/>
+      <c r="J88" s="4" t="inlineStr"/>
+      <c r="K88" s="4" t="inlineStr"/>
+      <c r="L88" s="4" t="inlineStr"/>
+      <c r="M88" s="4" t="inlineStr">
+        <is>
+          <t>RESTRICT</t>
+        </is>
+      </c>
+      <c r="N88" s="4" t="inlineStr">
         <is>
           <t>NO ACTION</t>
         </is>
       </c>
-      <c r="O88" s="6" t="inlineStr">
-        <is>
-          <t>Location the tag is installed in. NULL when not assigned.</t>
-        </is>
-      </c>
-      <c r="P88" s="6" t="inlineStr">
-        <is>
-          <t>Assumption: nullable, same as beacon.</t>
-        </is>
-      </c>
+      <c r="O88" s="4" t="inlineStr">
+        <is>
+          <t>How often the class repeats.</t>
+        </is>
+      </c>
+      <c r="P88" s="4" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>nfc_tags</t>
+          <t>class_schedule</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>payload_token</t>
+          <t>lecturer_id</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
@@ -4556,554 +4612,558 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr"/>
-      <c r="F89" s="4" t="inlineStr"/>
-      <c r="G89" s="4" t="inlineStr"/>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G89" s="4" t="inlineStr">
+        <is>
+          <t>users.id</t>
+        </is>
+      </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I89" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J89" s="4" t="inlineStr"/>
+      <c r="I89" s="4" t="inlineStr"/>
+      <c r="J89" s="4" t="inlineStr">
+        <is>
+          <t>uq_schedule_lecturer_slot</t>
+        </is>
+      </c>
       <c r="K89" s="4" t="inlineStr"/>
       <c r="L89" s="4" t="inlineStr"/>
-      <c r="M89" s="4" t="inlineStr"/>
-      <c r="N89" s="4" t="inlineStr"/>
+      <c r="M89" s="4" t="inlineStr">
+        <is>
+          <t>RESTRICT</t>
+        </is>
+      </c>
+      <c r="N89" s="4" t="inlineStr">
+        <is>
+          <t>CASCADE</t>
+        </is>
+      </c>
       <c r="O89" s="4" t="inlineStr">
         <is>
-          <t>Token written to the tag and validated by the server on tap.</t>
+          <t>Lecturer teaching the class (user with L prefix).</t>
         </is>
       </c>
       <c r="P89" s="4" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="5" t="inlineStr">
-        <is>
-          <t>nfc_tags</t>
-        </is>
-      </c>
-      <c r="B90" s="5" t="inlineStr">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>class_schedule</t>
+        </is>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>location_id</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="inlineStr"/>
+      <c r="E90" s="4" t="inlineStr"/>
+      <c r="F90" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G90" s="4" t="inlineStr">
+        <is>
+          <t>location.id</t>
+        </is>
+      </c>
+      <c r="H90" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I90" s="4" t="inlineStr"/>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>uq_schedule_location_slot</t>
+        </is>
+      </c>
+      <c r="K90" s="4" t="inlineStr"/>
+      <c r="L90" s="4" t="inlineStr"/>
+      <c r="M90" s="4" t="inlineStr">
+        <is>
+          <t>RESTRICT</t>
+        </is>
+      </c>
+      <c r="N90" s="4" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
+      <c r="O90" s="4" t="inlineStr">
+        <is>
+          <t>Default location of the class.</t>
+        </is>
+      </c>
+      <c r="P90" s="4" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>class_schedule</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>start_time</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>TIME</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr"/>
+      <c r="E91" s="4" t="inlineStr"/>
+      <c r="F91" s="4" t="inlineStr"/>
+      <c r="G91" s="4" t="inlineStr"/>
+      <c r="H91" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I91" s="4" t="inlineStr"/>
+      <c r="J91" s="4" t="inlineStr">
+        <is>
+          <t>uq_schedule_location_slot, uq_schedule_lecturer_slot</t>
+        </is>
+      </c>
+      <c r="K91" s="4" t="inlineStr"/>
+      <c r="L91" s="4" t="inlineStr"/>
+      <c r="M91" s="4" t="inlineStr"/>
+      <c r="N91" s="4" t="inlineStr"/>
+      <c r="O91" s="4" t="inlineStr">
+        <is>
+          <t>Start time of the class.</t>
+        </is>
+      </c>
+      <c r="P91" s="4" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>class_schedule</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>end_time</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>TIME</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="inlineStr"/>
+      <c r="E92" s="4" t="inlineStr"/>
+      <c r="F92" s="4" t="inlineStr"/>
+      <c r="G92" s="4" t="inlineStr"/>
+      <c r="H92" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I92" s="4" t="inlineStr"/>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>uq_schedule_location_slot, uq_schedule_lecturer_slot</t>
+        </is>
+      </c>
+      <c r="K92" s="4" t="inlineStr"/>
+      <c r="L92" s="4" t="inlineStr"/>
+      <c r="M92" s="4" t="inlineStr"/>
+      <c r="N92" s="4" t="inlineStr"/>
+      <c r="O92" s="4" t="inlineStr">
+        <is>
+          <t>End time. Must be after start_time.</t>
+        </is>
+      </c>
+      <c r="P92" s="4" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>class_schedule</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>week_day</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>SMALLINT</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr"/>
+      <c r="E93" s="4" t="inlineStr"/>
+      <c r="F93" s="4" t="inlineStr"/>
+      <c r="G93" s="4" t="inlineStr"/>
+      <c r="H93" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I93" s="4" t="inlineStr"/>
+      <c r="J93" s="4" t="inlineStr">
+        <is>
+          <t>uq_schedule_location_slot, uq_schedule_lecturer_slot</t>
+        </is>
+      </c>
+      <c r="K93" s="4" t="inlineStr"/>
+      <c r="L93" s="4" t="inlineStr">
+        <is>
+          <t>week_day BETWEEN 1 AND 7</t>
+        </is>
+      </c>
+      <c r="M93" s="4" t="inlineStr"/>
+      <c r="N93" s="4" t="inlineStr"/>
+      <c r="O93" s="4" t="inlineStr">
+        <is>
+          <t>ISO day of week: 1 = Monday ... 7 = Sunday. Matches EXTRACT(ISODOW FROM date).</t>
+        </is>
+      </c>
+      <c r="P93" s="4" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>class_schedule</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="C90" s="5" t="inlineStr">
+      <c r="C94" s="5" t="inlineStr">
         <is>
           <t>TIMESTAMPTZ</t>
         </is>
       </c>
-      <c r="D90" s="5" t="inlineStr"/>
-      <c r="E90" s="5" t="inlineStr"/>
-      <c r="F90" s="5" t="inlineStr"/>
-      <c r="G90" s="5" t="inlineStr"/>
-      <c r="H90" s="5" t="inlineStr">
+      <c r="D94" s="5" t="inlineStr"/>
+      <c r="E94" s="5" t="inlineStr"/>
+      <c r="F94" s="5" t="inlineStr"/>
+      <c r="G94" s="5" t="inlineStr"/>
+      <c r="H94" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I90" s="5" t="inlineStr"/>
-      <c r="J90" s="5" t="inlineStr"/>
-      <c r="K90" s="5" t="inlineStr">
+      <c r="I94" s="5" t="inlineStr"/>
+      <c r="J94" s="5" t="inlineStr"/>
+      <c r="K94" s="5" t="inlineStr">
         <is>
           <t>now()</t>
         </is>
       </c>
-      <c r="L90" s="5" t="inlineStr"/>
-      <c r="M90" s="5" t="inlineStr"/>
-      <c r="N90" s="5" t="inlineStr"/>
-      <c r="O90" s="5" t="inlineStr">
+      <c r="L94" s="5" t="inlineStr"/>
+      <c r="M94" s="5" t="inlineStr"/>
+      <c r="N94" s="5" t="inlineStr"/>
+      <c r="O94" s="5" t="inlineStr">
         <is>
           <t>When the row was created.</t>
         </is>
       </c>
-      <c r="P90" s="5" t="inlineStr">
+      <c r="P94" s="5" t="inlineStr">
         <is>
           <t>Audit column.</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="5" t="inlineStr">
-        <is>
-          <t>nfc_tags</t>
-        </is>
-      </c>
-      <c r="B91" s="5" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>class_schedule</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="C91" s="5" t="inlineStr">
+      <c r="C95" s="5" t="inlineStr">
         <is>
           <t>TIMESTAMPTZ</t>
         </is>
       </c>
-      <c r="D91" s="5" t="inlineStr"/>
-      <c r="E91" s="5" t="inlineStr"/>
-      <c r="F91" s="5" t="inlineStr"/>
-      <c r="G91" s="5" t="inlineStr"/>
-      <c r="H91" s="5" t="inlineStr">
+      <c r="D95" s="5" t="inlineStr"/>
+      <c r="E95" s="5" t="inlineStr"/>
+      <c r="F95" s="5" t="inlineStr"/>
+      <c r="G95" s="5" t="inlineStr"/>
+      <c r="H95" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I91" s="5" t="inlineStr"/>
-      <c r="J91" s="5" t="inlineStr"/>
-      <c r="K91" s="5" t="inlineStr">
+      <c r="I95" s="5" t="inlineStr"/>
+      <c r="J95" s="5" t="inlineStr"/>
+      <c r="K95" s="5" t="inlineStr">
         <is>
           <t>now()</t>
         </is>
       </c>
-      <c r="L91" s="5" t="inlineStr"/>
-      <c r="M91" s="5" t="inlineStr"/>
-      <c r="N91" s="5" t="inlineStr"/>
-      <c r="O91" s="5" t="inlineStr">
+      <c r="L95" s="5" t="inlineStr"/>
+      <c r="M95" s="5" t="inlineStr"/>
+      <c r="N95" s="5" t="inlineStr"/>
+      <c r="O95" s="5" t="inlineStr">
         <is>
           <t>When the row was last changed. Set automatically by trigger trg_&lt;table&gt;_updated_at.</t>
         </is>
       </c>
-      <c r="P91" s="5" t="inlineStr">
+      <c r="P95" s="5" t="inlineStr">
         <is>
           <t>Audit column.</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="5" t="inlineStr">
         <is>
           <t>class_schedule</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>Recurring timetable slot for a class in a period.</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="n"/>
-      <c r="D92" s="2" t="n"/>
-      <c r="E92" s="2" t="n"/>
-      <c r="F92" s="2" t="n"/>
-      <c r="G92" s="2" t="n"/>
-      <c r="H92" s="2" t="n"/>
-      <c r="I92" s="2" t="n"/>
-      <c r="J92" s="2" t="n"/>
-      <c r="K92" s="2" t="n"/>
-      <c r="L92" s="2" t="n"/>
-      <c r="M92" s="2" t="n"/>
-      <c r="N92" s="2" t="n"/>
-      <c r="O92" s="2" t="n"/>
-      <c r="P92" s="2" t="n"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="3" t="inlineStr">
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t>created_by</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D96" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E96" s="5" t="inlineStr"/>
+      <c r="F96" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G96" s="5" t="inlineStr">
+        <is>
+          <t>users.id</t>
+        </is>
+      </c>
+      <c r="H96" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I96" s="5" t="inlineStr"/>
+      <c r="J96" s="5" t="inlineStr"/>
+      <c r="K96" s="5" t="inlineStr"/>
+      <c r="L96" s="5" t="inlineStr"/>
+      <c r="M96" s="5" t="inlineStr">
+        <is>
+          <t>SET NULL</t>
+        </is>
+      </c>
+      <c r="N96" s="5" t="inlineStr">
+        <is>
+          <t>CASCADE</t>
+        </is>
+      </c>
+      <c r="O96" s="5" t="inlineStr">
+        <is>
+          <t>User who created the row. NULL for system-generated rows (e.g. automatic check-ins).</t>
+        </is>
+      </c>
+      <c r="P96" s="5" t="inlineStr">
+        <is>
+          <t>Audit column.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="inlineStr">
         <is>
           <t>class_schedule</t>
         </is>
       </c>
-      <c r="B93" s="3" t="inlineStr">
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>updated_by</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="inlineStr"/>
+      <c r="F97" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G97" s="5" t="inlineStr">
+        <is>
+          <t>users.id</t>
+        </is>
+      </c>
+      <c r="H97" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I97" s="5" t="inlineStr"/>
+      <c r="J97" s="5" t="inlineStr"/>
+      <c r="K97" s="5" t="inlineStr"/>
+      <c r="L97" s="5" t="inlineStr"/>
+      <c r="M97" s="5" t="inlineStr">
+        <is>
+          <t>SET NULL</t>
+        </is>
+      </c>
+      <c r="N97" s="5" t="inlineStr">
+        <is>
+          <t>CASCADE</t>
+        </is>
+      </c>
+      <c r="O97" s="5" t="inlineStr">
+        <is>
+          <t>User who last changed the row. Set by the application.</t>
+        </is>
+      </c>
+      <c r="P97" s="5" t="inlineStr">
+        <is>
+          <t>Audit column.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>class_session</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>A single occurrence of a scheduled class on a specific date.</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="n"/>
+      <c r="D98" s="2" t="n"/>
+      <c r="E98" s="2" t="n"/>
+      <c r="F98" s="2" t="n"/>
+      <c r="G98" s="2" t="n"/>
+      <c r="H98" s="2" t="n"/>
+      <c r="I98" s="2" t="n"/>
+      <c r="J98" s="2" t="n"/>
+      <c r="K98" s="2" t="n"/>
+      <c r="L98" s="2" t="n"/>
+      <c r="M98" s="2" t="n"/>
+      <c r="N98" s="2" t="n"/>
+      <c r="O98" s="2" t="n"/>
+      <c r="P98" s="2" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>class_session</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C93" s="3" t="inlineStr">
+      <c r="C99" s="3" t="inlineStr">
         <is>
           <t>INTEGER</t>
         </is>
       </c>
-      <c r="D93" s="3" t="inlineStr"/>
-      <c r="E93" s="3" t="inlineStr">
+      <c r="D99" s="3" t="inlineStr"/>
+      <c r="E99" s="3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F93" s="3" t="inlineStr"/>
-      <c r="G93" s="3" t="inlineStr"/>
-      <c r="H93" s="3" t="inlineStr">
+      <c r="F99" s="3" t="inlineStr"/>
+      <c r="G99" s="3" t="inlineStr"/>
+      <c r="H99" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I93" s="3" t="inlineStr">
+      <c r="I99" s="3" t="inlineStr">
         <is>
           <t>Yes (PK)</t>
         </is>
       </c>
-      <c r="J93" s="3" t="inlineStr"/>
-      <c r="K93" s="3" t="inlineStr">
+      <c r="J99" s="3" t="inlineStr"/>
+      <c r="K99" s="3" t="inlineStr">
         <is>
           <t>IDENTITY</t>
         </is>
       </c>
-      <c r="L93" s="3" t="inlineStr"/>
-      <c r="M93" s="3" t="inlineStr"/>
-      <c r="N93" s="3" t="inlineStr"/>
-      <c r="O93" s="3" t="inlineStr">
-        <is>
-          <t>Unique identifier of the schedule.</t>
-        </is>
-      </c>
-      <c r="P93" s="3" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="4" t="inlineStr">
-        <is>
-          <t>class_schedule</t>
-        </is>
-      </c>
-      <c r="B94" s="4" t="inlineStr">
-        <is>
-          <t>class_id</t>
-        </is>
-      </c>
-      <c r="C94" s="4" t="inlineStr">
-        <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="D94" s="4" t="inlineStr"/>
-      <c r="E94" s="4" t="inlineStr"/>
-      <c r="F94" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G94" s="4" t="inlineStr">
-        <is>
-          <t>class.id</t>
-        </is>
-      </c>
-      <c r="H94" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I94" s="4" t="inlineStr"/>
-      <c r="J94" s="4" t="inlineStr"/>
-      <c r="K94" s="4" t="inlineStr"/>
-      <c r="L94" s="4" t="inlineStr"/>
-      <c r="M94" s="4" t="inlineStr">
-        <is>
-          <t>RESTRICT</t>
-        </is>
-      </c>
-      <c r="N94" s="4" t="inlineStr">
-        <is>
-          <t>NO ACTION</t>
-        </is>
-      </c>
-      <c r="O94" s="4" t="inlineStr">
-        <is>
-          <t>Class being taught.</t>
-        </is>
-      </c>
-      <c r="P94" s="4" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="4" t="inlineStr">
-        <is>
-          <t>class_schedule</t>
-        </is>
-      </c>
-      <c r="B95" s="4" t="inlineStr">
-        <is>
-          <t>academic_period_id</t>
-        </is>
-      </c>
-      <c r="C95" s="4" t="inlineStr">
-        <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="D95" s="4" t="inlineStr"/>
-      <c r="E95" s="4" t="inlineStr"/>
-      <c r="F95" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G95" s="4" t="inlineStr">
-        <is>
-          <t>academic_period.id</t>
-        </is>
-      </c>
-      <c r="H95" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I95" s="4" t="inlineStr"/>
-      <c r="J95" s="4" t="inlineStr">
-        <is>
-          <t>uq_schedule_location_slot, uq_schedule_lecturer_slot</t>
-        </is>
-      </c>
-      <c r="K95" s="4" t="inlineStr"/>
-      <c r="L95" s="4" t="inlineStr"/>
-      <c r="M95" s="4" t="inlineStr">
-        <is>
-          <t>RESTRICT</t>
-        </is>
-      </c>
-      <c r="N95" s="4" t="inlineStr">
-        <is>
-          <t>NO ACTION</t>
-        </is>
-      </c>
-      <c r="O95" s="4" t="inlineStr">
-        <is>
-          <t>Period the schedule runs in.</t>
-        </is>
-      </c>
-      <c r="P95" s="4" t="inlineStr">
-        <is>
-          <t>Renamed from ERD 'periodId' for clarity.</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="4" t="inlineStr">
-        <is>
-          <t>class_schedule</t>
-        </is>
-      </c>
-      <c r="B96" s="4" t="inlineStr">
-        <is>
-          <t>frequency_id</t>
-        </is>
-      </c>
-      <c r="C96" s="4" t="inlineStr">
-        <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="D96" s="4" t="inlineStr"/>
-      <c r="E96" s="4" t="inlineStr"/>
-      <c r="F96" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G96" s="4" t="inlineStr">
-        <is>
-          <t>frequency.id</t>
-        </is>
-      </c>
-      <c r="H96" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I96" s="4" t="inlineStr"/>
-      <c r="J96" s="4" t="inlineStr"/>
-      <c r="K96" s="4" t="inlineStr"/>
-      <c r="L96" s="4" t="inlineStr"/>
-      <c r="M96" s="4" t="inlineStr">
-        <is>
-          <t>RESTRICT</t>
-        </is>
-      </c>
-      <c r="N96" s="4" t="inlineStr">
-        <is>
-          <t>NO ACTION</t>
-        </is>
-      </c>
-      <c r="O96" s="4" t="inlineStr">
-        <is>
-          <t>How often the class repeats.</t>
-        </is>
-      </c>
-      <c r="P96" s="4" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
-        <is>
-          <t>class_schedule</t>
-        </is>
-      </c>
-      <c r="B97" s="4" t="inlineStr">
-        <is>
-          <t>lecturer_id</t>
-        </is>
-      </c>
-      <c r="C97" s="4" t="inlineStr">
-        <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="D97" s="4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E97" s="4" t="inlineStr"/>
-      <c r="F97" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G97" s="4" t="inlineStr">
-        <is>
-          <t>users.id</t>
-        </is>
-      </c>
-      <c r="H97" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I97" s="4" t="inlineStr"/>
-      <c r="J97" s="4" t="inlineStr">
-        <is>
-          <t>uq_schedule_lecturer_slot</t>
-        </is>
-      </c>
-      <c r="K97" s="4" t="inlineStr"/>
-      <c r="L97" s="4" t="inlineStr"/>
-      <c r="M97" s="4" t="inlineStr">
-        <is>
-          <t>RESTRICT</t>
-        </is>
-      </c>
-      <c r="N97" s="4" t="inlineStr">
-        <is>
-          <t>CASCADE</t>
-        </is>
-      </c>
-      <c r="O97" s="4" t="inlineStr">
-        <is>
-          <t>Lecturer teaching the class (user with L prefix).</t>
-        </is>
-      </c>
-      <c r="P97" s="4" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="4" t="inlineStr">
-        <is>
-          <t>class_schedule</t>
-        </is>
-      </c>
-      <c r="B98" s="4" t="inlineStr">
-        <is>
-          <t>location_id</t>
-        </is>
-      </c>
-      <c r="C98" s="4" t="inlineStr">
-        <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="D98" s="4" t="inlineStr"/>
-      <c r="E98" s="4" t="inlineStr"/>
-      <c r="F98" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G98" s="4" t="inlineStr">
-        <is>
-          <t>location.id</t>
-        </is>
-      </c>
-      <c r="H98" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I98" s="4" t="inlineStr"/>
-      <c r="J98" s="4" t="inlineStr">
-        <is>
-          <t>uq_schedule_location_slot</t>
-        </is>
-      </c>
-      <c r="K98" s="4" t="inlineStr"/>
-      <c r="L98" s="4" t="inlineStr"/>
-      <c r="M98" s="4" t="inlineStr">
-        <is>
-          <t>RESTRICT</t>
-        </is>
-      </c>
-      <c r="N98" s="4" t="inlineStr">
-        <is>
-          <t>NO ACTION</t>
-        </is>
-      </c>
-      <c r="O98" s="4" t="inlineStr">
-        <is>
-          <t>Default location of the class.</t>
-        </is>
-      </c>
-      <c r="P98" s="4" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="4" t="inlineStr">
-        <is>
-          <t>class_schedule</t>
-        </is>
-      </c>
-      <c r="B99" s="4" t="inlineStr">
-        <is>
-          <t>start_time</t>
-        </is>
-      </c>
-      <c r="C99" s="4" t="inlineStr">
-        <is>
-          <t>TIME</t>
-        </is>
-      </c>
-      <c r="D99" s="4" t="inlineStr"/>
-      <c r="E99" s="4" t="inlineStr"/>
-      <c r="F99" s="4" t="inlineStr"/>
-      <c r="G99" s="4" t="inlineStr"/>
-      <c r="H99" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I99" s="4" t="inlineStr"/>
-      <c r="J99" s="4" t="inlineStr">
-        <is>
-          <t>uq_schedule_location_slot, uq_schedule_lecturer_slot</t>
-        </is>
-      </c>
-      <c r="K99" s="4" t="inlineStr"/>
-      <c r="L99" s="4" t="inlineStr"/>
-      <c r="M99" s="4" t="inlineStr"/>
-      <c r="N99" s="4" t="inlineStr"/>
-      <c r="O99" s="4" t="inlineStr">
-        <is>
-          <t>Start time of the class.</t>
-        </is>
-      </c>
-      <c r="P99" s="4" t="inlineStr"/>
+      <c r="L99" s="3" t="inlineStr"/>
+      <c r="M99" s="3" t="inlineStr"/>
+      <c r="N99" s="3" t="inlineStr"/>
+      <c r="O99" s="3" t="inlineStr">
+        <is>
+          <t>Unique identifier of the session.</t>
+        </is>
+      </c>
+      <c r="P99" s="3" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>class_schedule</t>
+          <t>class_session</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>end_time</t>
+          <t>class_schedule_id</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>TIME</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr"/>
       <c r="E100" s="4" t="inlineStr"/>
-      <c r="F100" s="4" t="inlineStr"/>
-      <c r="G100" s="4" t="inlineStr"/>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G100" s="4" t="inlineStr">
+        <is>
+          <t>class_schedule.id</t>
+        </is>
+      </c>
       <c r="H100" s="4" t="inlineStr">
         <is>
           <t>No</t>
@@ -5112,34 +5172,46 @@
       <c r="I100" s="4" t="inlineStr"/>
       <c r="J100" s="4" t="inlineStr">
         <is>
-          <t>uq_schedule_location_slot, uq_schedule_lecturer_slot</t>
+          <t>uq_session_schedule_date</t>
         </is>
       </c>
       <c r="K100" s="4" t="inlineStr"/>
       <c r="L100" s="4" t="inlineStr"/>
-      <c r="M100" s="4" t="inlineStr"/>
-      <c r="N100" s="4" t="inlineStr"/>
+      <c r="M100" s="4" t="inlineStr">
+        <is>
+          <t>RESTRICT</t>
+        </is>
+      </c>
+      <c r="N100" s="4" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
       <c r="O100" s="4" t="inlineStr">
         <is>
-          <t>End time. Must be after start_time.</t>
-        </is>
-      </c>
-      <c r="P100" s="4" t="inlineStr"/>
+          <t>Schedule this session belongs to.</t>
+        </is>
+      </c>
+      <c r="P100" s="4" t="inlineStr">
+        <is>
+          <t>Renamed from ERD 'scheduleId' to match enrollment.</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>class_schedule</t>
+          <t>class_session</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>week_day</t>
+          <t>session_date</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>SMALLINT</t>
+          <t>DATE</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr"/>
@@ -5154,542 +5226,550 @@
       <c r="I101" s="4" t="inlineStr"/>
       <c r="J101" s="4" t="inlineStr">
         <is>
-          <t>uq_schedule_location_slot, uq_schedule_lecturer_slot</t>
+          <t>uq_session_schedule_date</t>
         </is>
       </c>
       <c r="K101" s="4" t="inlineStr"/>
-      <c r="L101" s="4" t="inlineStr">
-        <is>
-          <t>week_day BETWEEN 1 AND 7</t>
-        </is>
-      </c>
+      <c r="L101" s="4" t="inlineStr"/>
       <c r="M101" s="4" t="inlineStr"/>
       <c r="N101" s="4" t="inlineStr"/>
       <c r="O101" s="4" t="inlineStr">
         <is>
-          <t>ISO day of week: 1 = Monday ... 7 = Sunday. Matches EXTRACT(ISODOW FROM date).</t>
-        </is>
-      </c>
-      <c r="P101" s="4" t="inlineStr"/>
+          <t>Date of the session.</t>
+        </is>
+      </c>
+      <c r="P101" s="4" t="inlineStr">
+        <is>
+          <t>Renamed from 'date' to avoid confusion with the DATE type.</t>
+        </is>
+      </c>
     </row>
     <row r="102">
-      <c r="A102" s="5" t="inlineStr">
-        <is>
-          <t>class_schedule</t>
-        </is>
-      </c>
-      <c r="B102" s="5" t="inlineStr">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>class_session</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>ENUM</t>
+        </is>
+      </c>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>session_status</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr"/>
+      <c r="F102" s="4" t="inlineStr"/>
+      <c r="G102" s="4" t="inlineStr"/>
+      <c r="H102" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I102" s="4" t="inlineStr"/>
+      <c r="J102" s="4" t="inlineStr"/>
+      <c r="K102" s="4" t="inlineStr">
+        <is>
+          <t>'scheduled'</t>
+        </is>
+      </c>
+      <c r="L102" s="4" t="inlineStr"/>
+      <c r="M102" s="4" t="inlineStr"/>
+      <c r="N102" s="4" t="inlineStr"/>
+      <c r="O102" s="4" t="inlineStr">
+        <is>
+          <t>scheduled, started, finished, rescheduled or cancelled.</t>
+        </is>
+      </c>
+      <c r="P102" s="4" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>class_session</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>override_start_time</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="inlineStr">
+        <is>
+          <t>TIME</t>
+        </is>
+      </c>
+      <c r="D103" s="4" t="inlineStr"/>
+      <c r="E103" s="4" t="inlineStr"/>
+      <c r="F103" s="4" t="inlineStr"/>
+      <c r="G103" s="4" t="inlineStr"/>
+      <c r="H103" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I103" s="4" t="inlineStr"/>
+      <c r="J103" s="4" t="inlineStr"/>
+      <c r="K103" s="4" t="inlineStr"/>
+      <c r="L103" s="4" t="inlineStr"/>
+      <c r="M103" s="4" t="inlineStr"/>
+      <c r="N103" s="4" t="inlineStr"/>
+      <c r="O103" s="4" t="inlineStr">
+        <is>
+          <t>Replaces the schedule start time for this session only.</t>
+        </is>
+      </c>
+      <c r="P103" s="4" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>class_session</t>
+        </is>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t>override_end_time</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t>TIME</t>
+        </is>
+      </c>
+      <c r="D104" s="4" t="inlineStr"/>
+      <c r="E104" s="4" t="inlineStr"/>
+      <c r="F104" s="4" t="inlineStr"/>
+      <c r="G104" s="4" t="inlineStr"/>
+      <c r="H104" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I104" s="4" t="inlineStr"/>
+      <c r="J104" s="4" t="inlineStr"/>
+      <c r="K104" s="4" t="inlineStr"/>
+      <c r="L104" s="4" t="inlineStr"/>
+      <c r="M104" s="4" t="inlineStr"/>
+      <c r="N104" s="4" t="inlineStr"/>
+      <c r="O104" s="4" t="inlineStr">
+        <is>
+          <t>Replaces the schedule end time for this session only.</t>
+        </is>
+      </c>
+      <c r="P104" s="4" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>class_session</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>override_location_id</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="D105" s="4" t="inlineStr"/>
+      <c r="E105" s="4" t="inlineStr"/>
+      <c r="F105" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G105" s="4" t="inlineStr">
+        <is>
+          <t>location.id</t>
+        </is>
+      </c>
+      <c r="H105" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I105" s="4" t="inlineStr"/>
+      <c r="J105" s="4" t="inlineStr"/>
+      <c r="K105" s="4" t="inlineStr"/>
+      <c r="L105" s="4" t="inlineStr"/>
+      <c r="M105" s="4" t="inlineStr">
+        <is>
+          <t>SET NULL</t>
+        </is>
+      </c>
+      <c r="N105" s="4" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
+      <c r="O105" s="4" t="inlineStr">
+        <is>
+          <t>Replaces the schedule location for this session only. NULL = use schedule location.</t>
+        </is>
+      </c>
+      <c r="P105" s="4" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="5" t="inlineStr">
+        <is>
+          <t>class_session</t>
+        </is>
+      </c>
+      <c r="B106" s="5" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="C102" s="5" t="inlineStr">
+      <c r="C106" s="5" t="inlineStr">
         <is>
           <t>TIMESTAMPTZ</t>
         </is>
       </c>
-      <c r="D102" s="5" t="inlineStr"/>
-      <c r="E102" s="5" t="inlineStr"/>
-      <c r="F102" s="5" t="inlineStr"/>
-      <c r="G102" s="5" t="inlineStr"/>
-      <c r="H102" s="5" t="inlineStr">
+      <c r="D106" s="5" t="inlineStr"/>
+      <c r="E106" s="5" t="inlineStr"/>
+      <c r="F106" s="5" t="inlineStr"/>
+      <c r="G106" s="5" t="inlineStr"/>
+      <c r="H106" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I102" s="5" t="inlineStr"/>
-      <c r="J102" s="5" t="inlineStr"/>
-      <c r="K102" s="5" t="inlineStr">
+      <c r="I106" s="5" t="inlineStr"/>
+      <c r="J106" s="5" t="inlineStr"/>
+      <c r="K106" s="5" t="inlineStr">
         <is>
           <t>now()</t>
         </is>
       </c>
-      <c r="L102" s="5" t="inlineStr"/>
-      <c r="M102" s="5" t="inlineStr"/>
-      <c r="N102" s="5" t="inlineStr"/>
-      <c r="O102" s="5" t="inlineStr">
+      <c r="L106" s="5" t="inlineStr"/>
+      <c r="M106" s="5" t="inlineStr"/>
+      <c r="N106" s="5" t="inlineStr"/>
+      <c r="O106" s="5" t="inlineStr">
         <is>
           <t>When the row was created.</t>
         </is>
       </c>
-      <c r="P102" s="5" t="inlineStr">
+      <c r="P106" s="5" t="inlineStr">
         <is>
           <t>Audit column.</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="5" t="inlineStr">
-        <is>
-          <t>class_schedule</t>
-        </is>
-      </c>
-      <c r="B103" s="5" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>class_session</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="C103" s="5" t="inlineStr">
+      <c r="C107" s="5" t="inlineStr">
         <is>
           <t>TIMESTAMPTZ</t>
         </is>
       </c>
-      <c r="D103" s="5" t="inlineStr"/>
-      <c r="E103" s="5" t="inlineStr"/>
-      <c r="F103" s="5" t="inlineStr"/>
-      <c r="G103" s="5" t="inlineStr"/>
-      <c r="H103" s="5" t="inlineStr">
+      <c r="D107" s="5" t="inlineStr"/>
+      <c r="E107" s="5" t="inlineStr"/>
+      <c r="F107" s="5" t="inlineStr"/>
+      <c r="G107" s="5" t="inlineStr"/>
+      <c r="H107" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I103" s="5" t="inlineStr"/>
-      <c r="J103" s="5" t="inlineStr"/>
-      <c r="K103" s="5" t="inlineStr">
+      <c r="I107" s="5" t="inlineStr"/>
+      <c r="J107" s="5" t="inlineStr"/>
+      <c r="K107" s="5" t="inlineStr">
         <is>
           <t>now()</t>
         </is>
       </c>
-      <c r="L103" s="5" t="inlineStr"/>
-      <c r="M103" s="5" t="inlineStr"/>
-      <c r="N103" s="5" t="inlineStr"/>
-      <c r="O103" s="5" t="inlineStr">
+      <c r="L107" s="5" t="inlineStr"/>
+      <c r="M107" s="5" t="inlineStr"/>
+      <c r="N107" s="5" t="inlineStr"/>
+      <c r="O107" s="5" t="inlineStr">
         <is>
           <t>When the row was last changed. Set automatically by trigger trg_&lt;table&gt;_updated_at.</t>
         </is>
       </c>
-      <c r="P103" s="5" t="inlineStr">
+      <c r="P107" s="5" t="inlineStr">
         <is>
           <t>Audit column.</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="5" t="inlineStr">
-        <is>
-          <t>class_schedule</t>
-        </is>
-      </c>
-      <c r="B104" s="5" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t>class_session</t>
+        </is>
+      </c>
+      <c r="B108" s="5" t="inlineStr">
         <is>
           <t>created_by</t>
         </is>
       </c>
-      <c r="C104" s="5" t="inlineStr">
+      <c r="C108" s="5" t="inlineStr">
         <is>
           <t>VARCHAR</t>
         </is>
       </c>
-      <c r="D104" s="5" t="inlineStr">
+      <c r="D108" s="5" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E104" s="5" t="inlineStr"/>
-      <c r="F104" s="5" t="inlineStr">
+      <c r="E108" s="5" t="inlineStr"/>
+      <c r="F108" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G104" s="5" t="inlineStr">
+      <c r="G108" s="5" t="inlineStr">
         <is>
           <t>users.id</t>
         </is>
       </c>
-      <c r="H104" s="5" t="inlineStr">
+      <c r="H108" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="I104" s="5" t="inlineStr"/>
-      <c r="J104" s="5" t="inlineStr"/>
-      <c r="K104" s="5" t="inlineStr"/>
-      <c r="L104" s="5" t="inlineStr"/>
-      <c r="M104" s="5" t="inlineStr">
+      <c r="I108" s="5" t="inlineStr"/>
+      <c r="J108" s="5" t="inlineStr"/>
+      <c r="K108" s="5" t="inlineStr"/>
+      <c r="L108" s="5" t="inlineStr"/>
+      <c r="M108" s="5" t="inlineStr">
         <is>
           <t>SET NULL</t>
         </is>
       </c>
-      <c r="N104" s="5" t="inlineStr">
+      <c r="N108" s="5" t="inlineStr">
         <is>
           <t>CASCADE</t>
         </is>
       </c>
-      <c r="O104" s="5" t="inlineStr">
+      <c r="O108" s="5" t="inlineStr">
         <is>
           <t>User who created the row. NULL for system-generated rows (e.g. automatic check-ins).</t>
         </is>
       </c>
-      <c r="P104" s="5" t="inlineStr">
+      <c r="P108" s="5" t="inlineStr">
         <is>
           <t>Audit column.</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="5" t="inlineStr">
-        <is>
-          <t>class_schedule</t>
-        </is>
-      </c>
-      <c r="B105" s="5" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t>class_session</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="inlineStr">
         <is>
           <t>updated_by</t>
         </is>
       </c>
-      <c r="C105" s="5" t="inlineStr">
+      <c r="C109" s="5" t="inlineStr">
         <is>
           <t>VARCHAR</t>
         </is>
       </c>
-      <c r="D105" s="5" t="inlineStr">
+      <c r="D109" s="5" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E105" s="5" t="inlineStr"/>
-      <c r="F105" s="5" t="inlineStr">
+      <c r="E109" s="5" t="inlineStr"/>
+      <c r="F109" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G105" s="5" t="inlineStr">
+      <c r="G109" s="5" t="inlineStr">
         <is>
           <t>users.id</t>
         </is>
       </c>
-      <c r="H105" s="5" t="inlineStr">
+      <c r="H109" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="I105" s="5" t="inlineStr"/>
-      <c r="J105" s="5" t="inlineStr"/>
-      <c r="K105" s="5" t="inlineStr"/>
-      <c r="L105" s="5" t="inlineStr"/>
-      <c r="M105" s="5" t="inlineStr">
+      <c r="I109" s="5" t="inlineStr"/>
+      <c r="J109" s="5" t="inlineStr"/>
+      <c r="K109" s="5" t="inlineStr"/>
+      <c r="L109" s="5" t="inlineStr"/>
+      <c r="M109" s="5" t="inlineStr">
         <is>
           <t>SET NULL</t>
         </is>
       </c>
-      <c r="N105" s="5" t="inlineStr">
+      <c r="N109" s="5" t="inlineStr">
         <is>
           <t>CASCADE</t>
         </is>
       </c>
-      <c r="O105" s="5" t="inlineStr">
+      <c r="O109" s="5" t="inlineStr">
         <is>
           <t>User who last changed the row. Set by the application.</t>
         </is>
       </c>
-      <c r="P105" s="5" t="inlineStr">
+      <c r="P109" s="5" t="inlineStr">
         <is>
           <t>Audit column.</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>class_session</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>A single occurrence of a scheduled class on a specific date.</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="n"/>
-      <c r="D106" s="2" t="n"/>
-      <c r="E106" s="2" t="n"/>
-      <c r="F106" s="2" t="n"/>
-      <c r="G106" s="2" t="n"/>
-      <c r="H106" s="2" t="n"/>
-      <c r="I106" s="2" t="n"/>
-      <c r="J106" s="2" t="n"/>
-      <c r="K106" s="2" t="n"/>
-      <c r="L106" s="2" t="n"/>
-      <c r="M106" s="2" t="n"/>
-      <c r="N106" s="2" t="n"/>
-      <c r="O106" s="2" t="n"/>
-      <c r="P106" s="2" t="n"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="3" t="inlineStr">
-        <is>
-          <t>class_session</t>
-        </is>
-      </c>
-      <c r="B107" s="3" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>enrollment</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Which students are enrolled in which scheduled class.</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="n"/>
+      <c r="D110" s="2" t="n"/>
+      <c r="E110" s="2" t="n"/>
+      <c r="F110" s="2" t="n"/>
+      <c r="G110" s="2" t="n"/>
+      <c r="H110" s="2" t="n"/>
+      <c r="I110" s="2" t="n"/>
+      <c r="J110" s="2" t="n"/>
+      <c r="K110" s="2" t="n"/>
+      <c r="L110" s="2" t="n"/>
+      <c r="M110" s="2" t="n"/>
+      <c r="N110" s="2" t="n"/>
+      <c r="O110" s="2" t="n"/>
+      <c r="P110" s="2" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>enrollment</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C107" s="3" t="inlineStr">
+      <c r="C111" s="3" t="inlineStr">
         <is>
           <t>INTEGER</t>
         </is>
       </c>
-      <c r="D107" s="3" t="inlineStr"/>
-      <c r="E107" s="3" t="inlineStr">
+      <c r="D111" s="3" t="inlineStr"/>
+      <c r="E111" s="3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F107" s="3" t="inlineStr"/>
-      <c r="G107" s="3" t="inlineStr"/>
-      <c r="H107" s="3" t="inlineStr">
+      <c r="F111" s="3" t="inlineStr"/>
+      <c r="G111" s="3" t="inlineStr"/>
+      <c r="H111" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I107" s="3" t="inlineStr">
+      <c r="I111" s="3" t="inlineStr">
         <is>
           <t>Yes (PK)</t>
         </is>
       </c>
-      <c r="J107" s="3" t="inlineStr"/>
-      <c r="K107" s="3" t="inlineStr">
+      <c r="J111" s="3" t="inlineStr"/>
+      <c r="K111" s="3" t="inlineStr">
         <is>
           <t>IDENTITY</t>
         </is>
       </c>
-      <c r="L107" s="3" t="inlineStr"/>
-      <c r="M107" s="3" t="inlineStr"/>
-      <c r="N107" s="3" t="inlineStr"/>
-      <c r="O107" s="3" t="inlineStr">
-        <is>
-          <t>Unique identifier of the session.</t>
-        </is>
-      </c>
-      <c r="P107" s="3" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="4" t="inlineStr">
-        <is>
-          <t>class_session</t>
-        </is>
-      </c>
-      <c r="B108" s="4" t="inlineStr">
-        <is>
-          <t>class_schedule_id</t>
-        </is>
-      </c>
-      <c r="C108" s="4" t="inlineStr">
-        <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="D108" s="4" t="inlineStr"/>
-      <c r="E108" s="4" t="inlineStr"/>
-      <c r="F108" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G108" s="4" t="inlineStr">
-        <is>
-          <t>class_schedule.id</t>
-        </is>
-      </c>
-      <c r="H108" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I108" s="4" t="inlineStr"/>
-      <c r="J108" s="4" t="inlineStr">
-        <is>
-          <t>uq_session_schedule_date</t>
-        </is>
-      </c>
-      <c r="K108" s="4" t="inlineStr"/>
-      <c r="L108" s="4" t="inlineStr"/>
-      <c r="M108" s="4" t="inlineStr">
-        <is>
-          <t>RESTRICT</t>
-        </is>
-      </c>
-      <c r="N108" s="4" t="inlineStr">
-        <is>
-          <t>NO ACTION</t>
-        </is>
-      </c>
-      <c r="O108" s="4" t="inlineStr">
-        <is>
-          <t>Schedule this session belongs to.</t>
-        </is>
-      </c>
-      <c r="P108" s="4" t="inlineStr">
-        <is>
-          <t>Renamed from ERD 'scheduleId' to match enrollment.</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="4" t="inlineStr">
-        <is>
-          <t>class_session</t>
-        </is>
-      </c>
-      <c r="B109" s="4" t="inlineStr">
-        <is>
-          <t>session_date</t>
-        </is>
-      </c>
-      <c r="C109" s="4" t="inlineStr">
-        <is>
-          <t>DATE</t>
-        </is>
-      </c>
-      <c r="D109" s="4" t="inlineStr"/>
-      <c r="E109" s="4" t="inlineStr"/>
-      <c r="F109" s="4" t="inlineStr"/>
-      <c r="G109" s="4" t="inlineStr"/>
-      <c r="H109" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I109" s="4" t="inlineStr"/>
-      <c r="J109" s="4" t="inlineStr">
-        <is>
-          <t>uq_session_schedule_date</t>
-        </is>
-      </c>
-      <c r="K109" s="4" t="inlineStr"/>
-      <c r="L109" s="4" t="inlineStr"/>
-      <c r="M109" s="4" t="inlineStr"/>
-      <c r="N109" s="4" t="inlineStr"/>
-      <c r="O109" s="4" t="inlineStr">
-        <is>
-          <t>Date of the session.</t>
-        </is>
-      </c>
-      <c r="P109" s="4" t="inlineStr">
-        <is>
-          <t>Renamed from 'date' to avoid confusion with the DATE type.</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="4" t="inlineStr">
-        <is>
-          <t>class_session</t>
-        </is>
-      </c>
-      <c r="B110" s="4" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="C110" s="4" t="inlineStr">
-        <is>
-          <t>ENUM</t>
-        </is>
-      </c>
-      <c r="D110" s="4" t="inlineStr">
-        <is>
-          <t>session_status</t>
-        </is>
-      </c>
-      <c r="E110" s="4" t="inlineStr"/>
-      <c r="F110" s="4" t="inlineStr"/>
-      <c r="G110" s="4" t="inlineStr"/>
-      <c r="H110" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I110" s="4" t="inlineStr"/>
-      <c r="J110" s="4" t="inlineStr"/>
-      <c r="K110" s="4" t="inlineStr">
-        <is>
-          <t>'scheduled'</t>
-        </is>
-      </c>
-      <c r="L110" s="4" t="inlineStr"/>
-      <c r="M110" s="4" t="inlineStr"/>
-      <c r="N110" s="4" t="inlineStr"/>
-      <c r="O110" s="4" t="inlineStr">
-        <is>
-          <t>scheduled, started, finished, rescheduled or cancelled.</t>
-        </is>
-      </c>
-      <c r="P110" s="4" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="4" t="inlineStr">
-        <is>
-          <t>class_session</t>
-        </is>
-      </c>
-      <c r="B111" s="4" t="inlineStr">
-        <is>
-          <t>override_start_time</t>
-        </is>
-      </c>
-      <c r="C111" s="4" t="inlineStr">
-        <is>
-          <t>TIME</t>
-        </is>
-      </c>
-      <c r="D111" s="4" t="inlineStr"/>
-      <c r="E111" s="4" t="inlineStr"/>
-      <c r="F111" s="4" t="inlineStr"/>
-      <c r="G111" s="4" t="inlineStr"/>
-      <c r="H111" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I111" s="4" t="inlineStr"/>
-      <c r="J111" s="4" t="inlineStr"/>
-      <c r="K111" s="4" t="inlineStr"/>
-      <c r="L111" s="4" t="inlineStr"/>
-      <c r="M111" s="4" t="inlineStr"/>
-      <c r="N111" s="4" t="inlineStr"/>
-      <c r="O111" s="4" t="inlineStr">
-        <is>
-          <t>Replaces the schedule start time for this session only.</t>
-        </is>
-      </c>
-      <c r="P111" s="4" t="inlineStr"/>
+      <c r="L111" s="3" t="inlineStr"/>
+      <c r="M111" s="3" t="inlineStr"/>
+      <c r="N111" s="3" t="inlineStr"/>
+      <c r="O111" s="3" t="inlineStr">
+        <is>
+          <t>Unique identifier of the enrollment.</t>
+        </is>
+      </c>
+      <c r="P111" s="3" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>class_session</t>
+          <t>enrollment</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>override_end_time</t>
+          <t>user_id</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>TIME</t>
-        </is>
-      </c>
-      <c r="D112" s="4" t="inlineStr"/>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D112" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="E112" s="4" t="inlineStr"/>
-      <c r="F112" s="4" t="inlineStr"/>
-      <c r="G112" s="4" t="inlineStr"/>
+      <c r="F112" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G112" s="4" t="inlineStr">
+        <is>
+          <t>users.id</t>
+        </is>
+      </c>
       <c r="H112" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I112" s="4" t="inlineStr"/>
-      <c r="J112" s="4" t="inlineStr"/>
+      <c r="J112" s="4" t="inlineStr">
+        <is>
+          <t>uq_enrollment_user_schedule</t>
+        </is>
+      </c>
       <c r="K112" s="4" t="inlineStr"/>
       <c r="L112" s="4" t="inlineStr"/>
-      <c r="M112" s="4" t="inlineStr"/>
-      <c r="N112" s="4" t="inlineStr"/>
+      <c r="M112" s="4" t="inlineStr">
+        <is>
+          <t>RESTRICT</t>
+        </is>
+      </c>
+      <c r="N112" s="4" t="inlineStr">
+        <is>
+          <t>CASCADE</t>
+        </is>
+      </c>
       <c r="O112" s="4" t="inlineStr">
         <is>
-          <t>Replaces the schedule end time for this session only.</t>
+          <t>Enrolled student.</t>
         </is>
       </c>
       <c r="P112" s="4" t="inlineStr"/>
@@ -5697,12 +5777,12 @@
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>class_session</t>
+          <t>enrollment</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>override_location_id</t>
+          <t>class_schedule_id</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
@@ -5719,21 +5799,25 @@
       </c>
       <c r="G113" s="4" t="inlineStr">
         <is>
-          <t>location.id</t>
+          <t>class_schedule.id</t>
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I113" s="4" t="inlineStr"/>
-      <c r="J113" s="4" t="inlineStr"/>
+      <c r="J113" s="4" t="inlineStr">
+        <is>
+          <t>uq_enrollment_user_schedule</t>
+        </is>
+      </c>
       <c r="K113" s="4" t="inlineStr"/>
       <c r="L113" s="4" t="inlineStr"/>
       <c r="M113" s="4" t="inlineStr">
         <is>
-          <t>SET NULL</t>
+          <t>RESTRICT</t>
         </is>
       </c>
       <c r="N113" s="4" t="inlineStr">
@@ -5743,7 +5827,7 @@
       </c>
       <c r="O113" s="4" t="inlineStr">
         <is>
-          <t>Replaces the schedule location for this session only. NULL = use schedule location.</t>
+          <t>Schedule the student is enrolled in.</t>
         </is>
       </c>
       <c r="P113" s="4" t="inlineStr"/>
@@ -5751,7 +5835,7 @@
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>class_session</t>
+          <t>enrollment</t>
         </is>
       </c>
       <c r="B114" s="5" t="inlineStr">
@@ -5797,7 +5881,7 @@
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>class_session</t>
+          <t>enrollment</t>
         </is>
       </c>
       <c r="B115" s="5" t="inlineStr">
@@ -5843,7 +5927,7 @@
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>class_session</t>
+          <t>enrollment</t>
         </is>
       </c>
       <c r="B116" s="5" t="inlineStr">
@@ -5905,7 +5989,7 @@
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>class_session</t>
+          <t>enrollment</t>
         </is>
       </c>
       <c r="B117" s="5" t="inlineStr">
@@ -5967,12 +6051,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>enrollment</t>
+          <t>attendance</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Which students are enrolled in which scheduled class.</t>
+          <t>A student's attendance record for one session.</t>
         </is>
       </c>
       <c r="C118" s="2" t="n"/>
@@ -5993,985 +6077,1175 @@
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>enrollment</t>
+          <t>attendance</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>student_id</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F119" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G119" s="3" t="inlineStr">
+        <is>
+          <t>users.id</t>
+        </is>
+      </c>
+      <c r="H119" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I119" s="3" t="inlineStr"/>
+      <c r="J119" s="3" t="inlineStr">
+        <is>
+          <t>pk_attendance</t>
+        </is>
+      </c>
+      <c r="K119" s="3" t="inlineStr"/>
+      <c r="L119" s="3" t="inlineStr"/>
+      <c r="M119" s="3" t="inlineStr">
+        <is>
+          <t>RESTRICT</t>
+        </is>
+      </c>
+      <c r="N119" s="3" t="inlineStr">
+        <is>
+          <t>CASCADE</t>
+        </is>
+      </c>
+      <c r="O119" s="3" t="inlineStr">
+        <is>
+          <t>Student the record belongs to.</t>
+        </is>
+      </c>
+      <c r="P119" s="3" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="inlineStr">
+        <is>
+          <t>attendance</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>session_id</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="inlineStr">
+        <is>
           <t>INTEGER</t>
         </is>
       </c>
-      <c r="D119" s="3" t="inlineStr"/>
-      <c r="E119" s="3" t="inlineStr">
+      <c r="D120" s="3" t="inlineStr"/>
+      <c r="E120" s="3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F119" s="3" t="inlineStr"/>
-      <c r="G119" s="3" t="inlineStr"/>
-      <c r="H119" s="3" t="inlineStr">
+      <c r="F120" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G120" s="3" t="inlineStr">
+        <is>
+          <t>class_session.id</t>
+        </is>
+      </c>
+      <c r="H120" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I119" s="3" t="inlineStr">
-        <is>
-          <t>Yes (PK)</t>
-        </is>
-      </c>
-      <c r="J119" s="3" t="inlineStr"/>
-      <c r="K119" s="3" t="inlineStr">
-        <is>
-          <t>IDENTITY</t>
-        </is>
-      </c>
-      <c r="L119" s="3" t="inlineStr"/>
-      <c r="M119" s="3" t="inlineStr"/>
-      <c r="N119" s="3" t="inlineStr"/>
-      <c r="O119" s="3" t="inlineStr">
-        <is>
-          <t>Unique identifier of the enrollment.</t>
-        </is>
-      </c>
-      <c r="P119" s="3" t="inlineStr"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="4" t="inlineStr">
-        <is>
-          <t>enrollment</t>
-        </is>
-      </c>
-      <c r="B120" s="4" t="inlineStr">
-        <is>
-          <t>user_id</t>
-        </is>
-      </c>
-      <c r="C120" s="4" t="inlineStr">
-        <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="D120" s="4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E120" s="4" t="inlineStr"/>
-      <c r="F120" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G120" s="4" t="inlineStr">
-        <is>
-          <t>users.id</t>
-        </is>
-      </c>
-      <c r="H120" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I120" s="4" t="inlineStr"/>
-      <c r="J120" s="4" t="inlineStr">
-        <is>
-          <t>uq_enrollment_user_schedule</t>
-        </is>
-      </c>
-      <c r="K120" s="4" t="inlineStr"/>
-      <c r="L120" s="4" t="inlineStr"/>
-      <c r="M120" s="4" t="inlineStr">
+      <c r="I120" s="3" t="inlineStr"/>
+      <c r="J120" s="3" t="inlineStr">
+        <is>
+          <t>pk_attendance</t>
+        </is>
+      </c>
+      <c r="K120" s="3" t="inlineStr"/>
+      <c r="L120" s="3" t="inlineStr"/>
+      <c r="M120" s="3" t="inlineStr">
         <is>
           <t>RESTRICT</t>
         </is>
       </c>
-      <c r="N120" s="4" t="inlineStr">
-        <is>
-          <t>CASCADE</t>
-        </is>
-      </c>
-      <c r="O120" s="4" t="inlineStr">
-        <is>
-          <t>Enrolled student.</t>
-        </is>
-      </c>
-      <c r="P120" s="4" t="inlineStr"/>
+      <c r="N120" s="3" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
+      <c r="O120" s="3" t="inlineStr">
+        <is>
+          <t>Session attended.</t>
+        </is>
+      </c>
+      <c r="P120" s="3" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>enrollment</t>
+          <t>attendance</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>class_schedule_id</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="D121" s="4" t="inlineStr"/>
+          <t>ENUM</t>
+        </is>
+      </c>
+      <c r="D121" s="4" t="inlineStr">
+        <is>
+          <t>attendance_status</t>
+        </is>
+      </c>
       <c r="E121" s="4" t="inlineStr"/>
-      <c r="F121" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G121" s="4" t="inlineStr">
-        <is>
-          <t>class_schedule.id</t>
-        </is>
-      </c>
+      <c r="F121" s="4" t="inlineStr"/>
+      <c r="G121" s="4" t="inlineStr"/>
       <c r="H121" s="4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
       <c r="I121" s="4" t="inlineStr"/>
-      <c r="J121" s="4" t="inlineStr">
-        <is>
-          <t>uq_enrollment_user_schedule</t>
-        </is>
-      </c>
+      <c r="J121" s="4" t="inlineStr"/>
       <c r="K121" s="4" t="inlineStr"/>
       <c r="L121" s="4" t="inlineStr"/>
-      <c r="M121" s="4" t="inlineStr">
-        <is>
-          <t>RESTRICT</t>
-        </is>
-      </c>
-      <c r="N121" s="4" t="inlineStr">
-        <is>
-          <t>NO ACTION</t>
-        </is>
-      </c>
+      <c r="M121" s="4" t="inlineStr"/>
+      <c r="N121" s="4" t="inlineStr"/>
       <c r="O121" s="4" t="inlineStr">
         <is>
-          <t>Schedule the student is enrolled in.</t>
+          <t>present, absent or late.</t>
         </is>
       </c>
       <c r="P121" s="4" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" s="5" t="inlineStr">
-        <is>
-          <t>enrollment</t>
-        </is>
-      </c>
-      <c r="B122" s="5" t="inlineStr">
-        <is>
-          <t>created_at</t>
-        </is>
-      </c>
-      <c r="C122" s="5" t="inlineStr">
+      <c r="A122" s="4" t="inlineStr">
+        <is>
+          <t>attendance</t>
+        </is>
+      </c>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
+          <t>checked_in_at</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="inlineStr">
         <is>
           <t>TIMESTAMPTZ</t>
         </is>
       </c>
-      <c r="D122" s="5" t="inlineStr"/>
-      <c r="E122" s="5" t="inlineStr"/>
-      <c r="F122" s="5" t="inlineStr"/>
-      <c r="G122" s="5" t="inlineStr"/>
-      <c r="H122" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I122" s="5" t="inlineStr"/>
-      <c r="J122" s="5" t="inlineStr"/>
-      <c r="K122" s="5" t="inlineStr">
-        <is>
-          <t>now()</t>
-        </is>
-      </c>
-      <c r="L122" s="5" t="inlineStr"/>
-      <c r="M122" s="5" t="inlineStr"/>
-      <c r="N122" s="5" t="inlineStr"/>
-      <c r="O122" s="5" t="inlineStr">
-        <is>
-          <t>When the row was created.</t>
-        </is>
-      </c>
-      <c r="P122" s="5" t="inlineStr">
-        <is>
-          <t>Audit column.</t>
-        </is>
-      </c>
+      <c r="D122" s="4" t="inlineStr"/>
+      <c r="E122" s="4" t="inlineStr"/>
+      <c r="F122" s="4" t="inlineStr"/>
+      <c r="G122" s="4" t="inlineStr"/>
+      <c r="H122" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I122" s="4" t="inlineStr"/>
+      <c r="J122" s="4" t="inlineStr"/>
+      <c r="K122" s="4" t="inlineStr"/>
+      <c r="L122" s="4" t="inlineStr"/>
+      <c r="M122" s="4" t="inlineStr"/>
+      <c r="N122" s="4" t="inlineStr"/>
+      <c r="O122" s="4" t="inlineStr">
+        <is>
+          <t>When the student checked in. NULL when absent.</t>
+        </is>
+      </c>
+      <c r="P122" s="4" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="5" t="inlineStr">
-        <is>
-          <t>enrollment</t>
-        </is>
-      </c>
-      <c r="B123" s="5" t="inlineStr">
-        <is>
-          <t>updated_at</t>
-        </is>
-      </c>
-      <c r="C123" s="5" t="inlineStr">
-        <is>
-          <t>TIMESTAMPTZ</t>
-        </is>
-      </c>
-      <c r="D123" s="5" t="inlineStr"/>
-      <c r="E123" s="5" t="inlineStr"/>
-      <c r="F123" s="5" t="inlineStr"/>
-      <c r="G123" s="5" t="inlineStr"/>
-      <c r="H123" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I123" s="5" t="inlineStr"/>
-      <c r="J123" s="5" t="inlineStr"/>
-      <c r="K123" s="5" t="inlineStr">
-        <is>
-          <t>now()</t>
-        </is>
-      </c>
-      <c r="L123" s="5" t="inlineStr"/>
-      <c r="M123" s="5" t="inlineStr"/>
-      <c r="N123" s="5" t="inlineStr"/>
-      <c r="O123" s="5" t="inlineStr">
-        <is>
-          <t>When the row was last changed. Set automatically by trigger trg_&lt;table&gt;_updated_at.</t>
-        </is>
-      </c>
-      <c r="P123" s="5" t="inlineStr">
-        <is>
-          <t>Audit column.</t>
+      <c r="A123" s="6" t="inlineStr">
+        <is>
+          <t>attendance</t>
+        </is>
+      </c>
+      <c r="B123" s="6" t="inlineStr">
+        <is>
+          <t>check_in_method</t>
+        </is>
+      </c>
+      <c r="C123" s="6" t="inlineStr">
+        <is>
+          <t>ENUM</t>
+        </is>
+      </c>
+      <c r="D123" s="6" t="inlineStr">
+        <is>
+          <t>check_in_method</t>
+        </is>
+      </c>
+      <c r="E123" s="6" t="inlineStr"/>
+      <c r="F123" s="6" t="inlineStr"/>
+      <c r="G123" s="6" t="inlineStr"/>
+      <c r="H123" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I123" s="6" t="inlineStr"/>
+      <c r="J123" s="6" t="inlineStr"/>
+      <c r="K123" s="6" t="inlineStr"/>
+      <c r="L123" s="6" t="inlineStr"/>
+      <c r="M123" s="6" t="inlineStr"/>
+      <c r="N123" s="6" t="inlineStr"/>
+      <c r="O123" s="6" t="inlineStr">
+        <is>
+          <t>How the check-in was made: beacon, nfc, qr or manual. NULL when absent.</t>
+        </is>
+      </c>
+      <c r="P123" s="6" t="inlineStr">
+        <is>
+          <t>Assumption: replaces ERD 'FK int: method' since no method table exists.</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="5" t="inlineStr">
-        <is>
-          <t>enrollment</t>
-        </is>
-      </c>
-      <c r="B124" s="5" t="inlineStr">
-        <is>
-          <t>created_by</t>
-        </is>
-      </c>
-      <c r="C124" s="5" t="inlineStr">
+      <c r="A124" s="4" t="inlineStr">
+        <is>
+          <t>attendance</t>
+        </is>
+      </c>
+      <c r="B124" s="4" t="inlineStr">
+        <is>
+          <t>comments</t>
+        </is>
+      </c>
+      <c r="C124" s="4" t="inlineStr">
         <is>
           <t>VARCHAR</t>
         </is>
       </c>
-      <c r="D124" s="5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E124" s="5" t="inlineStr"/>
-      <c r="F124" s="5" t="inlineStr">
+      <c r="D124" s="4" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="E124" s="4" t="inlineStr"/>
+      <c r="F124" s="4" t="inlineStr"/>
+      <c r="G124" s="4" t="inlineStr"/>
+      <c r="H124" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G124" s="5" t="inlineStr">
-        <is>
-          <t>users.id</t>
-        </is>
-      </c>
-      <c r="H124" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I124" s="5" t="inlineStr"/>
-      <c r="J124" s="5" t="inlineStr"/>
-      <c r="K124" s="5" t="inlineStr"/>
-      <c r="L124" s="5" t="inlineStr"/>
-      <c r="M124" s="5" t="inlineStr">
-        <is>
-          <t>SET NULL</t>
-        </is>
-      </c>
-      <c r="N124" s="5" t="inlineStr">
-        <is>
-          <t>CASCADE</t>
-        </is>
-      </c>
-      <c r="O124" s="5" t="inlineStr">
-        <is>
-          <t>User who created the row. NULL for system-generated rows (e.g. automatic check-ins).</t>
-        </is>
-      </c>
-      <c r="P124" s="5" t="inlineStr">
-        <is>
-          <t>Audit column.</t>
-        </is>
-      </c>
+      <c r="I124" s="4" t="inlineStr"/>
+      <c r="J124" s="4" t="inlineStr"/>
+      <c r="K124" s="4" t="inlineStr"/>
+      <c r="L124" s="4" t="inlineStr"/>
+      <c r="M124" s="4" t="inlineStr"/>
+      <c r="N124" s="4" t="inlineStr"/>
+      <c r="O124" s="4" t="inlineStr">
+        <is>
+          <t>Notes, e.g. reason for absence.</t>
+        </is>
+      </c>
+      <c r="P124" s="4" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>enrollment</t>
+          <t>attendance</t>
         </is>
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>updated_by</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="D125" s="5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>TIMESTAMPTZ</t>
+        </is>
+      </c>
+      <c r="D125" s="5" t="inlineStr"/>
       <c r="E125" s="5" t="inlineStr"/>
-      <c r="F125" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G125" s="5" t="inlineStr">
-        <is>
-          <t>users.id</t>
-        </is>
-      </c>
+      <c r="F125" s="5" t="inlineStr"/>
+      <c r="G125" s="5" t="inlineStr"/>
       <c r="H125" s="5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I125" s="5" t="inlineStr"/>
       <c r="J125" s="5" t="inlineStr"/>
-      <c r="K125" s="5" t="inlineStr"/>
+      <c r="K125" s="5" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
       <c r="L125" s="5" t="inlineStr"/>
-      <c r="M125" s="5" t="inlineStr">
+      <c r="M125" s="5" t="inlineStr"/>
+      <c r="N125" s="5" t="inlineStr"/>
+      <c r="O125" s="5" t="inlineStr">
+        <is>
+          <t>When the row was created.</t>
+        </is>
+      </c>
+      <c r="P125" s="5" t="inlineStr">
+        <is>
+          <t>Audit column.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="5" t="inlineStr">
+        <is>
+          <t>attendance</t>
+        </is>
+      </c>
+      <c r="B126" s="5" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="C126" s="5" t="inlineStr">
+        <is>
+          <t>TIMESTAMPTZ</t>
+        </is>
+      </c>
+      <c r="D126" s="5" t="inlineStr"/>
+      <c r="E126" s="5" t="inlineStr"/>
+      <c r="F126" s="5" t="inlineStr"/>
+      <c r="G126" s="5" t="inlineStr"/>
+      <c r="H126" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I126" s="5" t="inlineStr"/>
+      <c r="J126" s="5" t="inlineStr"/>
+      <c r="K126" s="5" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
+      <c r="L126" s="5" t="inlineStr"/>
+      <c r="M126" s="5" t="inlineStr"/>
+      <c r="N126" s="5" t="inlineStr"/>
+      <c r="O126" s="5" t="inlineStr">
+        <is>
+          <t>When the row was last changed. Set automatically by trigger trg_&lt;table&gt;_updated_at.</t>
+        </is>
+      </c>
+      <c r="P126" s="5" t="inlineStr">
+        <is>
+          <t>Audit column.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t>attendance</t>
+        </is>
+      </c>
+      <c r="B127" s="5" t="inlineStr">
+        <is>
+          <t>created_by</t>
+        </is>
+      </c>
+      <c r="C127" s="5" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D127" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E127" s="5" t="inlineStr"/>
+      <c r="F127" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G127" s="5" t="inlineStr">
+        <is>
+          <t>users.id</t>
+        </is>
+      </c>
+      <c r="H127" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I127" s="5" t="inlineStr"/>
+      <c r="J127" s="5" t="inlineStr"/>
+      <c r="K127" s="5" t="inlineStr"/>
+      <c r="L127" s="5" t="inlineStr"/>
+      <c r="M127" s="5" t="inlineStr">
         <is>
           <t>SET NULL</t>
         </is>
       </c>
-      <c r="N125" s="5" t="inlineStr">
+      <c r="N127" s="5" t="inlineStr">
         <is>
           <t>CASCADE</t>
         </is>
       </c>
-      <c r="O125" s="5" t="inlineStr">
+      <c r="O127" s="5" t="inlineStr">
+        <is>
+          <t>User who created the row. NULL for system-generated rows (e.g. automatic check-ins).</t>
+        </is>
+      </c>
+      <c r="P127" s="5" t="inlineStr">
+        <is>
+          <t>Audit column.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="5" t="inlineStr">
+        <is>
+          <t>attendance</t>
+        </is>
+      </c>
+      <c r="B128" s="5" t="inlineStr">
+        <is>
+          <t>updated_by</t>
+        </is>
+      </c>
+      <c r="C128" s="5" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D128" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E128" s="5" t="inlineStr"/>
+      <c r="F128" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G128" s="5" t="inlineStr">
+        <is>
+          <t>users.id</t>
+        </is>
+      </c>
+      <c r="H128" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I128" s="5" t="inlineStr"/>
+      <c r="J128" s="5" t="inlineStr"/>
+      <c r="K128" s="5" t="inlineStr"/>
+      <c r="L128" s="5" t="inlineStr"/>
+      <c r="M128" s="5" t="inlineStr">
+        <is>
+          <t>SET NULL</t>
+        </is>
+      </c>
+      <c r="N128" s="5" t="inlineStr">
+        <is>
+          <t>CASCADE</t>
+        </is>
+      </c>
+      <c r="O128" s="5" t="inlineStr">
         <is>
           <t>User who last changed the row. Set by the application.</t>
         </is>
       </c>
-      <c r="P125" s="5" t="inlineStr">
+      <c r="P128" s="5" t="inlineStr">
         <is>
           <t>Audit column.</t>
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
-        <is>
-          <t>attendance</t>
-        </is>
-      </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>A student's attendance record for one session.</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="n"/>
-      <c r="D126" s="2" t="n"/>
-      <c r="E126" s="2" t="n"/>
-      <c r="F126" s="2" t="n"/>
-      <c r="G126" s="2" t="n"/>
-      <c r="H126" s="2" t="n"/>
-      <c r="I126" s="2" t="n"/>
-      <c r="J126" s="2" t="n"/>
-      <c r="K126" s="2" t="n"/>
-      <c r="L126" s="2" t="n"/>
-      <c r="M126" s="2" t="n"/>
-      <c r="N126" s="2" t="n"/>
-      <c r="O126" s="2" t="n"/>
-      <c r="P126" s="2" t="n"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="3" t="inlineStr">
-        <is>
-          <t>attendance</t>
-        </is>
-      </c>
-      <c r="B127" s="3" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>attendance_audit</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>Append-only history of every change to an attendance record. Filled by trigger trg_attendance_audit.</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="n"/>
+      <c r="D129" s="2" t="n"/>
+      <c r="E129" s="2" t="n"/>
+      <c r="F129" s="2" t="n"/>
+      <c r="G129" s="2" t="n"/>
+      <c r="H129" s="2" t="n"/>
+      <c r="I129" s="2" t="n"/>
+      <c r="J129" s="2" t="n"/>
+      <c r="K129" s="2" t="n"/>
+      <c r="L129" s="2" t="n"/>
+      <c r="M129" s="2" t="n"/>
+      <c r="N129" s="2" t="n"/>
+      <c r="O129" s="2" t="n"/>
+      <c r="P129" s="2" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>attendance_audit</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="inlineStr"/>
+      <c r="E130" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F130" s="3" t="inlineStr"/>
+      <c r="G130" s="3" t="inlineStr"/>
+      <c r="H130" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I130" s="3" t="inlineStr">
+        <is>
+          <t>Yes (PK)</t>
+        </is>
+      </c>
+      <c r="J130" s="3" t="inlineStr"/>
+      <c r="K130" s="3" t="inlineStr">
+        <is>
+          <t>IDENTITY</t>
+        </is>
+      </c>
+      <c r="L130" s="3" t="inlineStr"/>
+      <c r="M130" s="3" t="inlineStr"/>
+      <c r="N130" s="3" t="inlineStr"/>
+      <c r="O130" s="3" t="inlineStr">
+        <is>
+          <t>Unique identifier of the history entry.</t>
+        </is>
+      </c>
+      <c r="P130" s="3" t="inlineStr">
+        <is>
+          <t>BIGINT because history grows with every change.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="4" t="inlineStr">
+        <is>
+          <t>attendance_audit</t>
+        </is>
+      </c>
+      <c r="B131" s="4" t="inlineStr">
         <is>
           <t>student_id</t>
         </is>
       </c>
-      <c r="C127" s="3" t="inlineStr">
+      <c r="C131" s="4" t="inlineStr">
         <is>
           <t>VARCHAR</t>
         </is>
       </c>
-      <c r="D127" s="3" t="inlineStr">
+      <c r="D131" s="4" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E127" s="3" t="inlineStr">
+      <c r="E131" s="4" t="inlineStr"/>
+      <c r="F131" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F127" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G127" s="3" t="inlineStr">
-        <is>
-          <t>users.id</t>
-        </is>
-      </c>
-      <c r="H127" s="3" t="inlineStr">
+      <c r="G131" s="4" t="inlineStr">
+        <is>
+          <t>attendance.student_id</t>
+        </is>
+      </c>
+      <c r="H131" s="4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I127" s="3" t="inlineStr"/>
-      <c r="J127" s="3" t="inlineStr">
-        <is>
-          <t>pk_attendance</t>
-        </is>
-      </c>
-      <c r="K127" s="3" t="inlineStr"/>
-      <c r="L127" s="3" t="inlineStr"/>
-      <c r="M127" s="3" t="inlineStr">
+      <c r="I131" s="4" t="inlineStr"/>
+      <c r="J131" s="4" t="inlineStr">
+        <is>
+          <t>fk_attendance_audit_attendance</t>
+        </is>
+      </c>
+      <c r="K131" s="4" t="inlineStr"/>
+      <c r="L131" s="4" t="inlineStr"/>
+      <c r="M131" s="4" t="inlineStr">
         <is>
           <t>RESTRICT</t>
         </is>
       </c>
-      <c r="N127" s="3" t="inlineStr">
+      <c r="N131" s="4" t="inlineStr">
         <is>
           <t>CASCADE</t>
         </is>
       </c>
-      <c r="O127" s="3" t="inlineStr">
-        <is>
-          <t>Student the record belongs to.</t>
-        </is>
-      </c>
-      <c r="P127" s="3" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="3" t="inlineStr">
-        <is>
-          <t>attendance</t>
-        </is>
-      </c>
-      <c r="B128" s="3" t="inlineStr">
-        <is>
-          <t>session_id</t>
-        </is>
-      </c>
-      <c r="C128" s="3" t="inlineStr">
-        <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="D128" s="3" t="inlineStr"/>
-      <c r="E128" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F128" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G128" s="3" t="inlineStr">
-        <is>
-          <t>class_session.id</t>
-        </is>
-      </c>
-      <c r="H128" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I128" s="3" t="inlineStr"/>
-      <c r="J128" s="3" t="inlineStr">
-        <is>
-          <t>pk_attendance</t>
-        </is>
-      </c>
-      <c r="K128" s="3" t="inlineStr"/>
-      <c r="L128" s="3" t="inlineStr"/>
-      <c r="M128" s="3" t="inlineStr">
-        <is>
-          <t>RESTRICT</t>
-        </is>
-      </c>
-      <c r="N128" s="3" t="inlineStr">
-        <is>
-          <t>NO ACTION</t>
-        </is>
-      </c>
-      <c r="O128" s="3" t="inlineStr">
-        <is>
-          <t>Session attended.</t>
-        </is>
-      </c>
-      <c r="P128" s="3" t="inlineStr"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="4" t="inlineStr">
-        <is>
-          <t>attendance</t>
-        </is>
-      </c>
-      <c r="B129" s="4" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="C129" s="4" t="inlineStr">
-        <is>
-          <t>ENUM</t>
-        </is>
-      </c>
-      <c r="D129" s="4" t="inlineStr">
-        <is>
-          <t>attendance_status</t>
-        </is>
-      </c>
-      <c r="E129" s="4" t="inlineStr"/>
-      <c r="F129" s="4" t="inlineStr"/>
-      <c r="G129" s="4" t="inlineStr"/>
-      <c r="H129" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I129" s="4" t="inlineStr"/>
-      <c r="J129" s="4" t="inlineStr"/>
-      <c r="K129" s="4" t="inlineStr"/>
-      <c r="L129" s="4" t="inlineStr"/>
-      <c r="M129" s="4" t="inlineStr"/>
-      <c r="N129" s="4" t="inlineStr"/>
-      <c r="O129" s="4" t="inlineStr">
-        <is>
-          <t>present, absent or late.</t>
-        </is>
-      </c>
-      <c r="P129" s="4" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="4" t="inlineStr">
-        <is>
-          <t>attendance</t>
-        </is>
-      </c>
-      <c r="B130" s="4" t="inlineStr">
-        <is>
-          <t>checked_in_at</t>
-        </is>
-      </c>
-      <c r="C130" s="4" t="inlineStr">
-        <is>
-          <t>TIMESTAMPTZ</t>
-        </is>
-      </c>
-      <c r="D130" s="4" t="inlineStr"/>
-      <c r="E130" s="4" t="inlineStr"/>
-      <c r="F130" s="4" t="inlineStr"/>
-      <c r="G130" s="4" t="inlineStr"/>
-      <c r="H130" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I130" s="4" t="inlineStr"/>
-      <c r="J130" s="4" t="inlineStr"/>
-      <c r="K130" s="4" t="inlineStr"/>
-      <c r="L130" s="4" t="inlineStr"/>
-      <c r="M130" s="4" t="inlineStr"/>
-      <c r="N130" s="4" t="inlineStr"/>
-      <c r="O130" s="4" t="inlineStr">
-        <is>
-          <t>When the student checked in. NULL when absent.</t>
-        </is>
-      </c>
-      <c r="P130" s="4" t="inlineStr"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="6" t="inlineStr">
-        <is>
-          <t>attendance</t>
-        </is>
-      </c>
-      <c r="B131" s="6" t="inlineStr">
-        <is>
-          <t>check_in_method</t>
-        </is>
-      </c>
-      <c r="C131" s="6" t="inlineStr">
-        <is>
-          <t>ENUM</t>
-        </is>
-      </c>
-      <c r="D131" s="6" t="inlineStr">
-        <is>
-          <t>check_in_method</t>
-        </is>
-      </c>
-      <c r="E131" s="6" t="inlineStr"/>
-      <c r="F131" s="6" t="inlineStr"/>
-      <c r="G131" s="6" t="inlineStr"/>
-      <c r="H131" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I131" s="6" t="inlineStr"/>
-      <c r="J131" s="6" t="inlineStr"/>
-      <c r="K131" s="6" t="inlineStr"/>
-      <c r="L131" s="6" t="inlineStr"/>
-      <c r="M131" s="6" t="inlineStr"/>
-      <c r="N131" s="6" t="inlineStr"/>
-      <c r="O131" s="6" t="inlineStr">
-        <is>
-          <t>How the check-in was made: beacon, nfc, qr or manual. NULL when absent.</t>
-        </is>
-      </c>
-      <c r="P131" s="6" t="inlineStr">
-        <is>
-          <t>Assumption: replaces ERD 'FK int: method' since no method table exists.</t>
+      <c r="O131" s="4" t="inlineStr">
+        <is>
+          <t>Student of the attendance record that changed.</t>
+        </is>
+      </c>
+      <c r="P131" s="4" t="inlineStr">
+        <is>
+          <t>Part of a composite FK to attendance (student_id, session_id).</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
         <is>
-          <t>attendance</t>
+          <t>attendance_audit</t>
         </is>
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>session_id</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="D132" s="4" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="D132" s="4" t="inlineStr"/>
       <c r="E132" s="4" t="inlineStr"/>
-      <c r="F132" s="4" t="inlineStr"/>
-      <c r="G132" s="4" t="inlineStr"/>
+      <c r="F132" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G132" s="4" t="inlineStr">
+        <is>
+          <t>attendance.session_id</t>
+        </is>
+      </c>
       <c r="H132" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I132" s="4" t="inlineStr"/>
-      <c r="J132" s="4" t="inlineStr"/>
+      <c r="J132" s="4" t="inlineStr">
+        <is>
+          <t>fk_attendance_audit_attendance</t>
+        </is>
+      </c>
       <c r="K132" s="4" t="inlineStr"/>
       <c r="L132" s="4" t="inlineStr"/>
-      <c r="M132" s="4" t="inlineStr"/>
-      <c r="N132" s="4" t="inlineStr"/>
+      <c r="M132" s="4" t="inlineStr">
+        <is>
+          <t>RESTRICT</t>
+        </is>
+      </c>
+      <c r="N132" s="4" t="inlineStr">
+        <is>
+          <t>CASCADE</t>
+        </is>
+      </c>
       <c r="O132" s="4" t="inlineStr">
         <is>
-          <t>Notes, e.g. reason for absence.</t>
-        </is>
-      </c>
-      <c r="P132" s="4" t="inlineStr"/>
+          <t>Session of the attendance record that changed.</t>
+        </is>
+      </c>
+      <c r="P132" s="4" t="inlineStr">
+        <is>
+          <t>Part of a composite FK to attendance (student_id, session_id).</t>
+        </is>
+      </c>
     </row>
     <row r="133">
-      <c r="A133" s="5" t="inlineStr">
-        <is>
-          <t>attendance</t>
-        </is>
-      </c>
-      <c r="B133" s="5" t="inlineStr">
-        <is>
-          <t>created_at</t>
-        </is>
-      </c>
-      <c r="C133" s="5" t="inlineStr">
+      <c r="A133" s="4" t="inlineStr">
+        <is>
+          <t>attendance_audit</t>
+        </is>
+      </c>
+      <c r="B133" s="4" t="inlineStr">
+        <is>
+          <t>old_status</t>
+        </is>
+      </c>
+      <c r="C133" s="4" t="inlineStr">
+        <is>
+          <t>ENUM</t>
+        </is>
+      </c>
+      <c r="D133" s="4" t="inlineStr">
+        <is>
+          <t>attendance_status</t>
+        </is>
+      </c>
+      <c r="E133" s="4" t="inlineStr"/>
+      <c r="F133" s="4" t="inlineStr"/>
+      <c r="G133" s="4" t="inlineStr"/>
+      <c r="H133" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I133" s="4" t="inlineStr"/>
+      <c r="J133" s="4" t="inlineStr"/>
+      <c r="K133" s="4" t="inlineStr"/>
+      <c r="L133" s="4" t="inlineStr"/>
+      <c r="M133" s="4" t="inlineStr"/>
+      <c r="N133" s="4" t="inlineStr"/>
+      <c r="O133" s="4" t="inlineStr">
+        <is>
+          <t>Status before the change. NULL when the record was just created.</t>
+        </is>
+      </c>
+      <c r="P133" s="4" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="4" t="inlineStr">
+        <is>
+          <t>attendance_audit</t>
+        </is>
+      </c>
+      <c r="B134" s="4" t="inlineStr">
+        <is>
+          <t>new_status</t>
+        </is>
+      </c>
+      <c r="C134" s="4" t="inlineStr">
+        <is>
+          <t>ENUM</t>
+        </is>
+      </c>
+      <c r="D134" s="4" t="inlineStr">
+        <is>
+          <t>attendance_status</t>
+        </is>
+      </c>
+      <c r="E134" s="4" t="inlineStr"/>
+      <c r="F134" s="4" t="inlineStr"/>
+      <c r="G134" s="4" t="inlineStr"/>
+      <c r="H134" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I134" s="4" t="inlineStr"/>
+      <c r="J134" s="4" t="inlineStr"/>
+      <c r="K134" s="4" t="inlineStr"/>
+      <c r="L134" s="4" t="inlineStr"/>
+      <c r="M134" s="4" t="inlineStr"/>
+      <c r="N134" s="4" t="inlineStr"/>
+      <c r="O134" s="4" t="inlineStr">
+        <is>
+          <t>Status after the change.</t>
+        </is>
+      </c>
+      <c r="P134" s="4" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="4" t="inlineStr">
+        <is>
+          <t>attendance_audit</t>
+        </is>
+      </c>
+      <c r="B135" s="4" t="inlineStr">
+        <is>
+          <t>old_checked_in_at</t>
+        </is>
+      </c>
+      <c r="C135" s="4" t="inlineStr">
         <is>
           <t>TIMESTAMPTZ</t>
         </is>
       </c>
-      <c r="D133" s="5" t="inlineStr"/>
-      <c r="E133" s="5" t="inlineStr"/>
-      <c r="F133" s="5" t="inlineStr"/>
-      <c r="G133" s="5" t="inlineStr"/>
-      <c r="H133" s="5" t="inlineStr">
+      <c r="D135" s="4" t="inlineStr"/>
+      <c r="E135" s="4" t="inlineStr"/>
+      <c r="F135" s="4" t="inlineStr"/>
+      <c r="G135" s="4" t="inlineStr"/>
+      <c r="H135" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I135" s="4" t="inlineStr"/>
+      <c r="J135" s="4" t="inlineStr"/>
+      <c r="K135" s="4" t="inlineStr"/>
+      <c r="L135" s="4" t="inlineStr"/>
+      <c r="M135" s="4" t="inlineStr"/>
+      <c r="N135" s="4" t="inlineStr"/>
+      <c r="O135" s="4" t="inlineStr">
+        <is>
+          <t>Check-in time before the change. NULL when created or absent.</t>
+        </is>
+      </c>
+      <c r="P135" s="4" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="4" t="inlineStr">
+        <is>
+          <t>attendance_audit</t>
+        </is>
+      </c>
+      <c r="B136" s="4" t="inlineStr">
+        <is>
+          <t>new_checked_in_at</t>
+        </is>
+      </c>
+      <c r="C136" s="4" t="inlineStr">
+        <is>
+          <t>TIMESTAMPTZ</t>
+        </is>
+      </c>
+      <c r="D136" s="4" t="inlineStr"/>
+      <c r="E136" s="4" t="inlineStr"/>
+      <c r="F136" s="4" t="inlineStr"/>
+      <c r="G136" s="4" t="inlineStr"/>
+      <c r="H136" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I136" s="4" t="inlineStr"/>
+      <c r="J136" s="4" t="inlineStr"/>
+      <c r="K136" s="4" t="inlineStr"/>
+      <c r="L136" s="4" t="inlineStr"/>
+      <c r="M136" s="4" t="inlineStr"/>
+      <c r="N136" s="4" t="inlineStr"/>
+      <c r="O136" s="4" t="inlineStr">
+        <is>
+          <t>Check-in time after the change. NULL when absent.</t>
+        </is>
+      </c>
+      <c r="P136" s="4" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="4" t="inlineStr">
+        <is>
+          <t>attendance_audit</t>
+        </is>
+      </c>
+      <c r="B137" s="4" t="inlineStr">
+        <is>
+          <t>old_check_in_method</t>
+        </is>
+      </c>
+      <c r="C137" s="4" t="inlineStr">
+        <is>
+          <t>ENUM</t>
+        </is>
+      </c>
+      <c r="D137" s="4" t="inlineStr">
+        <is>
+          <t>check_in_method</t>
+        </is>
+      </c>
+      <c r="E137" s="4" t="inlineStr"/>
+      <c r="F137" s="4" t="inlineStr"/>
+      <c r="G137" s="4" t="inlineStr"/>
+      <c r="H137" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I137" s="4" t="inlineStr"/>
+      <c r="J137" s="4" t="inlineStr"/>
+      <c r="K137" s="4" t="inlineStr"/>
+      <c r="L137" s="4" t="inlineStr"/>
+      <c r="M137" s="4" t="inlineStr"/>
+      <c r="N137" s="4" t="inlineStr"/>
+      <c r="O137" s="4" t="inlineStr">
+        <is>
+          <t>Check-in method before the change. NULL when created or absent.</t>
+        </is>
+      </c>
+      <c r="P137" s="4" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="4" t="inlineStr">
+        <is>
+          <t>attendance_audit</t>
+        </is>
+      </c>
+      <c r="B138" s="4" t="inlineStr">
+        <is>
+          <t>new_check_in_method</t>
+        </is>
+      </c>
+      <c r="C138" s="4" t="inlineStr">
+        <is>
+          <t>ENUM</t>
+        </is>
+      </c>
+      <c r="D138" s="4" t="inlineStr">
+        <is>
+          <t>check_in_method</t>
+        </is>
+      </c>
+      <c r="E138" s="4" t="inlineStr"/>
+      <c r="F138" s="4" t="inlineStr"/>
+      <c r="G138" s="4" t="inlineStr"/>
+      <c r="H138" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I138" s="4" t="inlineStr"/>
+      <c r="J138" s="4" t="inlineStr"/>
+      <c r="K138" s="4" t="inlineStr"/>
+      <c r="L138" s="4" t="inlineStr"/>
+      <c r="M138" s="4" t="inlineStr"/>
+      <c r="N138" s="4" t="inlineStr"/>
+      <c r="O138" s="4" t="inlineStr">
+        <is>
+          <t>Check-in method after the change. NULL when absent.</t>
+        </is>
+      </c>
+      <c r="P138" s="4" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="4" t="inlineStr">
+        <is>
+          <t>attendance_audit</t>
+        </is>
+      </c>
+      <c r="B139" s="4" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+      <c r="C139" s="4" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D139" s="4" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="E139" s="4" t="inlineStr"/>
+      <c r="F139" s="4" t="inlineStr"/>
+      <c r="G139" s="4" t="inlineStr"/>
+      <c r="H139" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I139" s="4" t="inlineStr"/>
+      <c r="J139" s="4" t="inlineStr"/>
+      <c r="K139" s="4" t="inlineStr"/>
+      <c r="L139" s="4" t="inlineStr"/>
+      <c r="M139" s="4" t="inlineStr"/>
+      <c r="N139" s="4" t="inlineStr"/>
+      <c r="O139" s="4" t="inlineStr">
+        <is>
+          <t>Reason given for the change (copied from attendance.comments at the time).</t>
+        </is>
+      </c>
+      <c r="P139" s="4" t="inlineStr">
+        <is>
+          <t>Required by the application for manual changes (FR-07).</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="4" t="inlineStr">
+        <is>
+          <t>attendance_audit</t>
+        </is>
+      </c>
+      <c r="B140" s="4" t="inlineStr">
+        <is>
+          <t>changed_by</t>
+        </is>
+      </c>
+      <c r="C140" s="4" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D140" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E140" s="4" t="inlineStr"/>
+      <c r="F140" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G140" s="4" t="inlineStr">
+        <is>
+          <t>users.id</t>
+        </is>
+      </c>
+      <c r="H140" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I140" s="4" t="inlineStr"/>
+      <c r="J140" s="4" t="inlineStr"/>
+      <c r="K140" s="4" t="inlineStr"/>
+      <c r="L140" s="4" t="inlineStr"/>
+      <c r="M140" s="4" t="inlineStr">
+        <is>
+          <t>SET NULL</t>
+        </is>
+      </c>
+      <c r="N140" s="4" t="inlineStr">
+        <is>
+          <t>CASCADE</t>
+        </is>
+      </c>
+      <c r="O140" s="4" t="inlineStr">
+        <is>
+          <t>User who made the change (attendance.updated_by, or created_by on insert). NULL for system-generated changes.</t>
+        </is>
+      </c>
+      <c r="P140" s="4" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="5" t="inlineStr">
+        <is>
+          <t>attendance_audit</t>
+        </is>
+      </c>
+      <c r="B141" s="5" t="inlineStr">
+        <is>
+          <t>changed_at</t>
+        </is>
+      </c>
+      <c r="C141" s="5" t="inlineStr">
+        <is>
+          <t>TIMESTAMPTZ</t>
+        </is>
+      </c>
+      <c r="D141" s="5" t="inlineStr"/>
+      <c r="E141" s="5" t="inlineStr"/>
+      <c r="F141" s="5" t="inlineStr"/>
+      <c r="G141" s="5" t="inlineStr"/>
+      <c r="H141" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I133" s="5" t="inlineStr"/>
-      <c r="J133" s="5" t="inlineStr"/>
-      <c r="K133" s="5" t="inlineStr">
+      <c r="I141" s="5" t="inlineStr"/>
+      <c r="J141" s="5" t="inlineStr"/>
+      <c r="K141" s="5" t="inlineStr">
         <is>
           <t>now()</t>
         </is>
       </c>
-      <c r="L133" s="5" t="inlineStr"/>
-      <c r="M133" s="5" t="inlineStr"/>
-      <c r="N133" s="5" t="inlineStr"/>
-      <c r="O133" s="5" t="inlineStr">
-        <is>
-          <t>When the row was created.</t>
-        </is>
-      </c>
-      <c r="P133" s="5" t="inlineStr">
+      <c r="L141" s="5" t="inlineStr"/>
+      <c r="M141" s="5" t="inlineStr"/>
+      <c r="N141" s="5" t="inlineStr"/>
+      <c r="O141" s="5" t="inlineStr">
+        <is>
+          <t>When the change was made.</t>
+        </is>
+      </c>
+      <c r="P141" s="5" t="inlineStr">
         <is>
           <t>Audit column.</t>
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="5" t="inlineStr">
-        <is>
-          <t>attendance</t>
-        </is>
-      </c>
-      <c r="B134" s="5" t="inlineStr">
-        <is>
-          <t>updated_at</t>
-        </is>
-      </c>
-      <c r="C134" s="5" t="inlineStr">
-        <is>
-          <t>TIMESTAMPTZ</t>
-        </is>
-      </c>
-      <c r="D134" s="5" t="inlineStr"/>
-      <c r="E134" s="5" t="inlineStr"/>
-      <c r="F134" s="5" t="inlineStr"/>
-      <c r="G134" s="5" t="inlineStr"/>
-      <c r="H134" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I134" s="5" t="inlineStr"/>
-      <c r="J134" s="5" t="inlineStr"/>
-      <c r="K134" s="5" t="inlineStr">
-        <is>
-          <t>now()</t>
-        </is>
-      </c>
-      <c r="L134" s="5" t="inlineStr"/>
-      <c r="M134" s="5" t="inlineStr"/>
-      <c r="N134" s="5" t="inlineStr"/>
-      <c r="O134" s="5" t="inlineStr">
-        <is>
-          <t>When the row was last changed. Set automatically by trigger trg_&lt;table&gt;_updated_at.</t>
-        </is>
-      </c>
-      <c r="P134" s="5" t="inlineStr">
-        <is>
-          <t>Audit column.</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="5" t="inlineStr">
-        <is>
-          <t>attendance</t>
-        </is>
-      </c>
-      <c r="B135" s="5" t="inlineStr">
-        <is>
-          <t>created_by</t>
-        </is>
-      </c>
-      <c r="C135" s="5" t="inlineStr">
-        <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="D135" s="5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E135" s="5" t="inlineStr"/>
-      <c r="F135" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G135" s="5" t="inlineStr">
-        <is>
-          <t>users.id</t>
-        </is>
-      </c>
-      <c r="H135" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I135" s="5" t="inlineStr"/>
-      <c r="J135" s="5" t="inlineStr"/>
-      <c r="K135" s="5" t="inlineStr"/>
-      <c r="L135" s="5" t="inlineStr"/>
-      <c r="M135" s="5" t="inlineStr">
-        <is>
-          <t>SET NULL</t>
-        </is>
-      </c>
-      <c r="N135" s="5" t="inlineStr">
-        <is>
-          <t>CASCADE</t>
-        </is>
-      </c>
-      <c r="O135" s="5" t="inlineStr">
-        <is>
-          <t>User who created the row. NULL for system-generated rows (e.g. automatic check-ins).</t>
-        </is>
-      </c>
-      <c r="P135" s="5" t="inlineStr">
-        <is>
-          <t>Audit column.</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="5" t="inlineStr">
-        <is>
-          <t>attendance</t>
-        </is>
-      </c>
-      <c r="B136" s="5" t="inlineStr">
-        <is>
-          <t>updated_by</t>
-        </is>
-      </c>
-      <c r="C136" s="5" t="inlineStr">
-        <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="D136" s="5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E136" s="5" t="inlineStr"/>
-      <c r="F136" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G136" s="5" t="inlineStr">
-        <is>
-          <t>users.id</t>
-        </is>
-      </c>
-      <c r="H136" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I136" s="5" t="inlineStr"/>
-      <c r="J136" s="5" t="inlineStr"/>
-      <c r="K136" s="5" t="inlineStr"/>
-      <c r="L136" s="5" t="inlineStr"/>
-      <c r="M136" s="5" t="inlineStr">
-        <is>
-          <t>SET NULL</t>
-        </is>
-      </c>
-      <c r="N136" s="5" t="inlineStr">
-        <is>
-          <t>CASCADE</t>
-        </is>
-      </c>
-      <c r="O136" s="5" t="inlineStr">
-        <is>
-          <t>User who last changed the row. Set by the application.</t>
-        </is>
-      </c>
-      <c r="P136" s="5" t="inlineStr">
-        <is>
-          <t>Audit column.</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="7" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="7" t="inlineStr">
         <is>
           <t>Legend</t>
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="8" t="inlineStr"/>
-      <c r="B139" s="9" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="8" t="inlineStr"/>
+      <c r="B144" s="9" t="inlineStr">
         <is>
           <t>Primary key column</t>
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="10" t="inlineStr"/>
-      <c r="B140" s="9" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="10" t="inlineStr"/>
+      <c r="B145" s="9" t="inlineStr">
         <is>
           <t>Contains an assumption to confirm</t>
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="11" t="inlineStr"/>
-      <c r="B141" s="9" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="11" t="inlineStr"/>
+      <c r="B146" s="9" t="inlineStr">
         <is>
           <t>Audit column</t>
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="12" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="12" t="inlineStr">
         <is>
           <t>Composite Constraint lists the multi-column rule(s) the column belongs to; see the Composite Constraints tab.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P136"/>
+  <autoFilter ref="A1:P141"/>
   <mergeCells count="17">
-    <mergeCell ref="B29:P29"/>
-    <mergeCell ref="B77:P77"/>
     <mergeCell ref="B2:P2"/>
+    <mergeCell ref="B8:P8"/>
+    <mergeCell ref="B14:P14"/>
     <mergeCell ref="B20:P20"/>
-    <mergeCell ref="B106:P106"/>
-    <mergeCell ref="B14:P14"/>
-    <mergeCell ref="B37:P37"/>
-    <mergeCell ref="B126:P126"/>
-    <mergeCell ref="B53:P53"/>
+    <mergeCell ref="B30:P30"/>
+    <mergeCell ref="B38:P38"/>
+    <mergeCell ref="B45:P45"/>
+    <mergeCell ref="B49:P49"/>
     <mergeCell ref="B57:P57"/>
-    <mergeCell ref="B8:P8"/>
-    <mergeCell ref="B71:P71"/>
-    <mergeCell ref="B65:P65"/>
+    <mergeCell ref="B63:P63"/>
+    <mergeCell ref="B69:P69"/>
+    <mergeCell ref="B78:P78"/>
+    <mergeCell ref="B84:P84"/>
+    <mergeCell ref="B98:P98"/>
+    <mergeCell ref="B110:P110"/>
     <mergeCell ref="B118:P118"/>
-    <mergeCell ref="B92:P92"/>
-    <mergeCell ref="B44:P44"/>
-    <mergeCell ref="B86:P86"/>
+    <mergeCell ref="B129:P129"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6983,7 +7257,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -7307,12 +7581,12 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>chk_auth_tokens_expiry</t>
+          <t>chk_academic_period_dates</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>auth_tokens</t>
+          <t>academic_period</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -7322,34 +7596,34 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>created_at, expires_at</t>
+          <t>start_date, finish_date</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>expires_at &gt; created_at</t>
+          <t>finish_date &gt; start_date</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>A token must expire after it was created.</t>
+          <t>A period must finish after it starts.</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>ALTER TABLE auth_tokens ADD CONSTRAINT chk_auth_tokens_expiry CHECK (expires_at &gt; created_at);</t>
+          <t>ALTER TABLE academic_period ADD CONSTRAINT chk_academic_period_dates CHECK (finish_date &gt; start_date);</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>chk_academic_period_dates</t>
+          <t>chk_schedule_times</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>academic_period</t>
+          <t>class_schedule</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -7359,34 +7633,34 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>start_date, finish_date</t>
+          <t>start_time, end_time</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>finish_date &gt; start_date</t>
+          <t>end_time &gt; start_time</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>A period must finish after it starts.</t>
+          <t>A class must end after it starts.</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>ALTER TABLE academic_period ADD CONSTRAINT chk_academic_period_dates CHECK (finish_date &gt; start_date);</t>
+          <t>ALTER TABLE class_schedule ADD CONSTRAINT chk_schedule_times CHECK (end_time &gt; start_time);</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>chk_schedule_times</t>
+          <t>chk_session_override_times</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>class_schedule</t>
+          <t>class_session</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -7396,34 +7670,34 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>start_time, end_time</t>
+          <t>override_start_time, override_end_time</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>end_time &gt; start_time</t>
+          <t>override_start_time IS NULL OR override_end_time IS NULL OR override_end_time &gt; override_start_time</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>A class must end after it starts.</t>
+          <t>If both override times are set, end must be after start.</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>ALTER TABLE class_schedule ADD CONSTRAINT chk_schedule_times CHECK (end_time &gt; start_time);</t>
+          <t>ALTER TABLE class_session ADD CONSTRAINT chk_session_override_times CHECK (override_start_time IS NULL OR override_end_time IS NULL OR override_end_time &gt; override_start_time);</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>chk_session_override_times</t>
+          <t>chk_attendance_check_in</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>class_session</t>
+          <t>attendance</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -7433,92 +7707,121 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>override_start_time, override_end_time</t>
+          <t>status, checked_in_at, check_in_method</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>override_start_time IS NULL OR override_end_time IS NULL OR override_end_time &gt; override_start_time</t>
+          <t>(status = 'absent' AND checked_in_at IS NULL AND check_in_method IS NULL) OR (status &lt;&gt; 'absent' AND checked_in_at IS NOT NULL AND check_in_method IS NOT NULL)</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>If both override times are set, end must be after start.</t>
+          <t>Present or late requires a check-in time and method; absent must have neither. (Assumption)</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>ALTER TABLE class_session ADD CONSTRAINT chk_session_override_times CHECK (override_start_time IS NULL OR override_end_time IS NULL OR override_end_time &gt; override_start_time);</t>
+          <t>ALTER TABLE attendance ADD CONSTRAINT chk_attendance_check_in CHECK ((status = 'absent' AND checked_in_at IS NULL AND check_in_method IS NULL) OR (status &lt;&gt; 'absent' AND checked_in_at IS NOT NULL AND check_in_method IS NOT NULL));</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>chk_attendance_check_in</t>
+          <t>uq_users_email_lower</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>attendance</t>
+          <t>users</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>CHECK</t>
+          <t>UNIQUE INDEX</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>status, checked_in_at, check_in_method</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>(status = 'absent' AND checked_in_at IS NULL AND check_in_method IS NULL) OR (status &lt;&gt; 'absent' AND checked_in_at IS NOT NULL AND check_in_method IS NOT NULL)</t>
-        </is>
-      </c>
+          <t>LOWER(email)</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr"/>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Present or late requires a check-in time and method; absent must have neither. (Assumption)</t>
+          <t>Makes email unique ignoring case (Seb@x.com = seb@x.com).</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>ALTER TABLE attendance ADD CONSTRAINT chk_attendance_check_in CHECK ((status = 'absent' AND checked_in_at IS NULL AND check_in_method IS NULL) OR (status &lt;&gt; 'absent' AND checked_in_at IS NOT NULL AND check_in_method IS NOT NULL));</t>
+          <t>CREATE UNIQUE INDEX uq_users_email_lower ON users (LOWER(email));</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>uq_users_email_lower</t>
+          <t>fk_attendance_audit_attendance</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>users</t>
+          <t>attendance_audit</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>UNIQUE INDEX</t>
+          <t>FOREIGN KEY</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>LOWER(email)</t>
+          <t>student_id, session_id</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr"/>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Makes email unique ignoring case (Seb@x.com = seb@x.com).</t>
+          <t>Every history row points at an existing attendance record (the student + session pair).</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>CREATE UNIQUE INDEX uq_users_email_lower ON users (LOWER(email));</t>
+          <t>ALTER TABLE attendance_audit ADD CONSTRAINT fk_attendance_audit_attendance FOREIGN KEY (student_id, session_id) REFERENCES attendance (student_id, session_id) ON DELETE RESTRICT ON UPDATE CASCADE;</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>ix_attendance_audit_record</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>attendance_audit</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>INDEX</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>student_id, session_id, changed_at</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>Fast lookup of the history of one attendance record, oldest to newest.</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>CREATE INDEX ix_attendance_audit_record ON attendance_audit (student_id, session_id, changed_at);</t>
         </is>
       </c>
     </row>
@@ -7533,7 +7836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7691,27 +7994,27 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
+          <t>auth.users</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
           <t>users</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>user_permission</t>
-        </is>
-      </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>user_id</t>
+          <t>auth_user_id</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>1 : M</t>
+          <t>1 : 1</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -7721,24 +8024,24 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>CASCADE</t>
+          <t>RESTRICT</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>CASCADE</t>
+          <t>NO ACTION</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>User the override applies to.</t>
+          <t>Supabase Auth identity the user signs in with.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>permissions</t>
+          <t>users</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -7753,7 +8056,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>permission_id</t>
+          <t>user_id</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -7773,19 +8076,19 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>NO ACTION</t>
+          <t>CASCADE</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>Permission being granted or denied.</t>
+          <t>User the override applies to.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>users</t>
+          <t>permissions</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -7800,7 +8103,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>created_by</t>
+          <t>permission_id</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -7810,22 +8113,22 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>SET NULL</t>
+          <t>CASCADE</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>CASCADE</t>
+          <t>NO ACTION</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>User who created the row. NULL for system-generated rows (e.g. automatic check-ins).</t>
+          <t>Permission being granted or denied.</t>
         </is>
       </c>
     </row>
@@ -7847,7 +8150,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>updated_by</t>
+          <t>created_by</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -7872,14 +8175,14 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>User who last changed the row. Set by the application.</t>
+          <t>User who created the row. NULL for system-generated rows (e.g. automatic check-ins).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>users</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -7889,12 +8192,12 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>role_permission</t>
+          <t>user_permission</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>role_id</t>
+          <t>updated_by</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -7904,29 +8207,29 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Mandatory</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
+          <t>SET NULL</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
           <t>CASCADE</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>NO ACTION</t>
-        </is>
-      </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>Role receiving the permission.</t>
+          <t>User who last changed the row. Set by the application.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>permissions</t>
+          <t>role</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -7941,7 +8244,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>permission_id</t>
+          <t>role_id</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -7966,14 +8269,14 @@
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>Permission given to the role.</t>
+          <t>Role receiving the permission.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>users</t>
+          <t>permissions</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -7988,7 +8291,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>created_by</t>
+          <t>permission_id</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -7998,22 +8301,22 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>SET NULL</t>
+          <t>CASCADE</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>CASCADE</t>
+          <t>NO ACTION</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>User who created the row. NULL for system-generated rows (e.g. automatic check-ins).</t>
+          <t>Permission given to the role.</t>
         </is>
       </c>
     </row>
@@ -8035,7 +8338,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>updated_by</t>
+          <t>created_by</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -8060,7 +8363,7 @@
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>User who last changed the row. Set by the application.</t>
+          <t>User who created the row. NULL for system-generated rows (e.g. automatic check-ins).</t>
         </is>
       </c>
     </row>
@@ -8077,12 +8380,12 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>auth_tokens</t>
+          <t>role_permission</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>user_id</t>
+          <t>updated_by</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -8092,22 +8395,22 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Mandatory</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
+          <t>SET NULL</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
           <t>CASCADE</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>CASCADE</t>
-        </is>
-      </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>User the token was issued to.</t>
+          <t>User who last changed the row. Set by the application.</t>
         </is>
       </c>
     </row>
@@ -9095,6 +9398,100 @@
       <c r="I33" s="4" t="inlineStr">
         <is>
           <t>User who last changed the row. Set by the application.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>attendance</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>student_id, session_id</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>attendance_audit</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>student_id, session_id</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>1 : M</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>RESTRICT</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>CASCADE</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>Attendance record whose changes are logged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>users</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>attendance_audit</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>changed_by</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>1 : M</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>SET NULL</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>CASCADE</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>User who made the change. NULL for system-generated changes.</t>
         </is>
       </c>
     </row>
@@ -9186,7 +9583,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>attendance.status</t>
+          <t>attendance.status, attendance_audit.old_status, attendance_audit.new_status</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -9213,7 +9610,7 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>attendance.check_in_method</t>
+          <t>attendance.check_in_method, attendance_audit.old_check_in_method, attendance_audit.new_check_in_method</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -9292,7 +9689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -9572,6 +9969,40 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Table added</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>attendance_audit</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Append-only history of attendance changes (old and new status, time, method, reason, who, when). Written only by trigger trg_attendance_audit and protected by trg_attendance_audit_immutable. Satisfies FR-07 (every change records who made it and why).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Table removed</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>auth_tokens</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Replaced by Supabase Auth (auth.users). users.auth_user_id links each user to their sign-in identity.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
